--- a/converted_files/835/835-all-files.xlsx
+++ b/converted_files/835/835-all-files.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4602</t>
+          <t>69e82c67836d7d05c9a02206</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4634</t>
+          <t>69e82c67836d7d05c9a02238</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4634</t>
+          <t>69e82c67836d7d05c9a02238</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2283,7 +2283,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4634</t>
+          <t>69e82c67836d7d05c9a02238</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2535,7 +2535,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4661</t>
+          <t>69e82c67836d7d05c9a02265</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2995,7 +2995,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69e82c67836d7d05c9a022be</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69e82c67836d7d05c9a022be</t>
         </is>
       </c>
       <c r="B8"/>
@@ -3917,7 +3917,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69e82c67836d7d05c9a022be</t>
         </is>
       </c>
       <c r="B9"/>
@@ -4181,7 +4181,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69e82c67836d7d05c9a022be</t>
         </is>
       </c>
       <c r="B10"/>
@@ -4445,7 +4445,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69e82c67836d7d05c9a022be</t>
         </is>
       </c>
       <c r="B11"/>
@@ -4739,7 +4739,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ec</t>
+          <t>69e82c67836d7d05c9a022f0</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ed</t>
+          <t>69e82c67836d7d05c9a022f1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -5607,7 +5607,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f471b</t>
+          <t>69e82c67836d7d05c9a0231f</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69e82c67836d7d05c9a0238c</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6771,7 +6771,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69e82c67836d7d05c9a0238c</t>
         </is>
       </c>
       <c r="B16"/>
@@ -7035,7 +7035,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69e82c67836d7d05c9a0238c</t>
         </is>
       </c>
       <c r="B17"/>
@@ -7299,7 +7299,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69e82c67836d7d05c9a0238c</t>
         </is>
       </c>
       <c r="B18"/>
@@ -7563,7 +7563,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69e82c67836d7d05c9a0238c</t>
         </is>
       </c>
       <c r="B19"/>
@@ -7811,7 +7811,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69e82c67836d7d05c9a0238c</t>
         </is>
       </c>
       <c r="B20"/>
@@ -8105,7 +8105,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69e82c67836d7d05c9a0238c</t>
         </is>
       </c>
       <c r="B21"/>

--- a/converted_files/835/835-all-files.xlsx
+++ b/converted_files/835/835-all-files.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4602</t>
+          <t>69efef04ad4799caa7f5b053</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4634</t>
+          <t>69efef04ad4799caa7f5b085</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4634</t>
+          <t>69efef04ad4799caa7f5b085</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2283,7 +2283,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4634</t>
+          <t>69efef04ad4799caa7f5b085</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2535,7 +2535,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4661</t>
+          <t>69efef04ad4799caa7f5b0b2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2995,7 +2995,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69efef04ad4799caa7f5b10b</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69efef04ad4799caa7f5b10b</t>
         </is>
       </c>
       <c r="B8"/>
@@ -3917,7 +3917,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69efef04ad4799caa7f5b10b</t>
         </is>
       </c>
       <c r="B9"/>
@@ -4181,7 +4181,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69efef04ad4799caa7f5b10b</t>
         </is>
       </c>
       <c r="B10"/>
@@ -4445,7 +4445,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ba</t>
+          <t>69efef04ad4799caa7f5b10b</t>
         </is>
       </c>
       <c r="B11"/>
@@ -4739,7 +4739,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ec</t>
+          <t>69efef04ad4799caa7f5b13d</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f46ed</t>
+          <t>69efef04ad4799caa7f5b13e</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -5607,7 +5607,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f471b</t>
+          <t>69efef04ad4799caa7f5b16c</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69efef04ad4799caa7f5b1d9</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6771,7 +6771,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69efef04ad4799caa7f5b1d9</t>
         </is>
       </c>
       <c r="B16"/>
@@ -7035,7 +7035,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69efef04ad4799caa7f5b1d9</t>
         </is>
       </c>
       <c r="B17"/>
@@ -7299,7 +7299,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69efef04ad4799caa7f5b1d9</t>
         </is>
       </c>
       <c r="B18"/>
@@ -7563,7 +7563,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69efef04ad4799caa7f5b1d9</t>
         </is>
       </c>
       <c r="B19"/>
@@ -7811,7 +7811,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69efef04ad4799caa7f5b1d9</t>
         </is>
       </c>
       <c r="B20"/>
@@ -8105,7 +8105,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4788</t>
+          <t>69efef04ad4799caa7f5b1d9</t>
         </is>
       </c>
       <c r="B21"/>

--- a/converted_files/835/835-all-files.xlsx
+++ b/converted_files/835/835-all-files.xlsx
@@ -59,7 +59,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:GZ21"/>
+  <dimension ref="A1:GZ22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02206</t>
+          <t>6a04cbecb80b363c8541f061</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>835-provider-level-adjustment.dat</t>
+          <t>835-validation-issues.edi</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>800.0</v>
+        <v>700.0</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>500.0</v>
@@ -1168,7 +1168,7 @@
       <c r="O2"/>
       <c r="P2"/>
       <c r="Q2" s="1" t="n">
-        <v>500.0</v>
+        <v>132.0</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
@@ -1182,22 +1182,14 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>RECEIVER_ACCT_1</t>
+          <t>456</t>
         </is>
       </c>
       <c r="U2" s="4" t="n">
-        <v>45651.0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>CHECK_1</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>PAYER_ID</t>
-        </is>
-      </c>
+        <v>43555.0</v>
+      </c>
+      <c r="V2"/>
+      <c r="W2"/>
       <c r="X2" s="4" t="n">
         <v>45649.0</v>
       </c>
@@ -1224,80 +1216,44 @@
       <c r="AQ2"/>
       <c r="AR2"/>
       <c r="AS2"/>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>ADDNL_PAYER_ID</t>
-        </is>
-      </c>
+      <c r="AT2"/>
+      <c r="AU2"/>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>ANY PLAN USA</t>
+          <t>DELTA DENTAL OF ABC</t>
         </is>
       </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
-          <t>1 WALK THIS WAY</t>
+          <t>225 MAIN STREET</t>
         </is>
       </c>
       <c r="AX2"/>
       <c r="AY2" s="3" t="inlineStr">
         <is>
-          <t>ANYCITY</t>
+          <t>CENTERVILLE</t>
         </is>
       </c>
       <c r="AZ2" s="3" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="BA2" s="3" t="inlineStr">
         <is>
-          <t>45209</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="BB2"/>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>8661112222</t>
-        </is>
-      </c>
+      <c r="BC2"/>
+      <c r="BD2"/>
       <c r="BE2"/>
       <c r="BF2"/>
-      <c r="BG2" s="3" t="inlineStr">
-        <is>
-          <t>EDI</t>
-        </is>
-      </c>
-      <c r="BH2" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="BI2" s="3" t="inlineStr">
-        <is>
-          <t>8002223333</t>
-        </is>
-      </c>
-      <c r="BJ2" s="3" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="BK2" s="3" t="inlineStr">
-        <is>
-          <t>EDI.SUPPORT@ANYPAYER.COM</t>
-        </is>
-      </c>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
       <c r="BL2" s="3" t="inlineStr">
         <is>
           <t>PAYER_IDENTIFICATION_NUMBER</t>
@@ -1305,7 +1261,7 @@
       </c>
       <c r="BM2" s="3" t="inlineStr">
         <is>
-          <t>ADDNL_PAYER_ID</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="BN2"/>
@@ -1473,7 +1429,7 @@
         <v>800.0</v>
       </c>
       <c r="ER2" s="1" t="n">
-        <v>500.0</v>
+        <v>400.0</v>
       </c>
       <c r="ES2" t="n">
         <v>1.0</v>
@@ -1569,7 +1525,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02238</t>
+          <t>6a04cbecb80b363c8541f0c6</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1579,17 +1535,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>claim_adj_reason.dat</t>
+          <t>835-provider-level-adjustment.dat</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>10060875</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>PATACCT</t>
+          <t>5554555444</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1598,20 +1554,22 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>400.0</v>
+        <v>800.0</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="I3"/>
+        <v>500.0</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>300.0</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>CLAIMNUMBER</t>
+          <t>94060555410000</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1628,7 +1586,7 @@
       <c r="O3"/>
       <c r="P3"/>
       <c r="Q3" s="1" t="n">
-        <v>80.0</v>
+        <v>500.0</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
@@ -1640,25 +1598,29 @@
           <t>CHECK</t>
         </is>
       </c>
-      <c r="T3"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVER_ACCT_1</t>
+        </is>
+      </c>
       <c r="U3" s="4" t="n">
-        <v>43693.0</v>
+        <v>45651.0</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>CK NUMBER 1</t>
+          <t>CHECK_1</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>PAYER_ID</t>
         </is>
       </c>
       <c r="X3" s="4" t="n">
-        <v>43704.0</v>
+        <v>45649.0</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>320.0</v>
+        <v>300.0</v>
       </c>
       <c r="Z3"/>
       <c r="AA3"/>
@@ -1687,7 +1649,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>ADDNL_PAYER_ID</t>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
@@ -1754,8 +1716,16 @@
           <t>EDI.SUPPORT@ANYPAYER.COM</t>
         </is>
       </c>
-      <c r="BL3"/>
-      <c r="BM3"/>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BM3" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="BN3"/>
       <c r="BO3"/>
       <c r="BP3" s="3" t="inlineStr">
@@ -1765,7 +1735,7 @@
       </c>
       <c r="BQ3" s="3" t="inlineStr">
         <is>
-          <t>1123454567</t>
+          <t>PROVIDER2_NPI</t>
         </is>
       </c>
       <c r="BR3" s="3" t="inlineStr">
@@ -1795,8 +1765,16 @@
         </is>
       </c>
       <c r="BX3"/>
-      <c r="BY3"/>
-      <c r="BZ3"/>
+      <c r="BY3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BZ3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID2</t>
+        </is>
+      </c>
       <c r="CA3"/>
       <c r="CB3"/>
       <c r="CC3" s="3" t="inlineStr">
@@ -1806,24 +1784,20 @@
       </c>
       <c r="CD3" s="3" t="inlineStr">
         <is>
-          <t>ABC123456789</t>
+          <t>33344555510</t>
         </is>
       </c>
       <c r="CE3" s="3" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>BUDD</t>
         </is>
       </c>
       <c r="CF3" s="3" t="inlineStr">
         <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CG3" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>WILLIAM</t>
+        </is>
+      </c>
+      <c r="CG3"/>
       <c r="CH3" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -1831,24 +1805,20 @@
       </c>
       <c r="CI3" s="3" t="inlineStr">
         <is>
-          <t>ABC123456789</t>
+          <t>33344555510</t>
         </is>
       </c>
       <c r="CJ3" s="3" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>BUDD</t>
         </is>
       </c>
       <c r="CK3" s="3" t="inlineStr">
         <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CL3" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>WILLIAM</t>
+        </is>
+      </c>
+      <c r="CL3"/>
       <c r="CM3"/>
       <c r="CN3"/>
       <c r="CO3"/>
@@ -1880,33 +1850,19 @@
       <c r="DO3"/>
       <c r="DP3"/>
       <c r="DQ3" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="DR3" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="DS3"/>
       <c r="DT3"/>
       <c r="DU3"/>
-      <c r="DV3" s="4" t="n">
-        <v>43505.0</v>
-      </c>
-      <c r="DW3" s="1" t="n">
-        <v>150.0</v>
-      </c>
-      <c r="DX3" s="3" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="DY3" s="3" t="inlineStr">
-        <is>
-          <t>COVERAGE_AMOUNT</t>
-        </is>
-      </c>
-      <c r="DZ3" s="1" t="n">
-        <v>150.0</v>
-      </c>
+      <c r="DV3"/>
+      <c r="DW3"/>
+      <c r="DX3"/>
+      <c r="DY3"/>
+      <c r="DZ3"/>
       <c r="EA3"/>
       <c r="EB3"/>
       <c r="EC3"/>
@@ -1923,7 +1879,7 @@
       </c>
       <c r="EK3" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>99211</t>
         </is>
       </c>
       <c r="EL3"/>
@@ -1932,10 +1888,10 @@
       <c r="EO3"/>
       <c r="EP3"/>
       <c r="EQ3" s="1" t="n">
-        <v>150.0</v>
+        <v>800.0</v>
       </c>
       <c r="ER3" s="1" t="n">
-        <v>80.0</v>
+        <v>500.0</v>
       </c>
       <c r="ES3" t="n">
         <v>1.0</v>
@@ -1948,26 +1904,26 @@
       <c r="EY3"/>
       <c r="EZ3"/>
       <c r="FA3" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="FB3" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="FC3" s="1" t="n">
-        <v>70.0</v>
+        <v>300.0</v>
       </c>
       <c r="FD3" s="3" t="inlineStr">
         <is>
-          <t>CONTRACTUAL</t>
+          <t>PATIENT_RESPONSIBILITY</t>
         </is>
       </c>
       <c r="FE3" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FF3" s="1" t="n">
-        <v>70.0</v>
+        <v>300.0</v>
       </c>
       <c r="FG3"/>
       <c r="FH3"/>
@@ -1998,7 +1954,7 @@
       <c r="GG3"/>
       <c r="GH3"/>
       <c r="GI3" s="1" t="n">
-        <v>80.0</v>
+        <v>800.0</v>
       </c>
       <c r="GJ3" s="3" t="inlineStr">
         <is>
@@ -2011,7 +1967,7 @@
         </is>
       </c>
       <c r="GL3" s="1" t="n">
-        <v>80.0</v>
+        <v>800.0</v>
       </c>
       <c r="GM3"/>
       <c r="GN3"/>
@@ -2031,41 +1987,97 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02238</t>
-        </is>
-      </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
+          <t>6a04cbecb80b363c8541f0f8</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>claim_adj_reason.dat</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>10060875</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>PATACCT</t>
         </is>
       </c>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>400.0</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>80.0</v>
+      </c>
       <c r="I4"/>
-      <c r="J4"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>CLAIMNUMBER</t>
         </is>
       </c>
-      <c r="L4"/>
-      <c r="M4"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N4"/>
       <c r="O4"/>
       <c r="P4"/>
-      <c r="Q4"/>
-      <c r="R4"/>
-      <c r="S4"/>
+      <c r="Q4" s="1" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="T4"/>
-      <c r="U4"/>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
+      <c r="U4" s="4" t="n">
+        <v>43693.0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>CK NUMBER 1</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>43704.0</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>320.0</v>
+      </c>
       <c r="Z4"/>
       <c r="AA4"/>
       <c r="AB4"/>
@@ -2086,51 +2098,175 @@
       <c r="AQ4"/>
       <c r="AR4"/>
       <c r="AS4"/>
-      <c r="AT4"/>
-      <c r="AU4"/>
-      <c r="AV4"/>
-      <c r="AW4"/>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
       <c r="AX4"/>
-      <c r="AY4"/>
-      <c r="AZ4"/>
-      <c r="BA4"/>
+      <c r="AY4" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="AZ4" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="BA4" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
       <c r="BB4"/>
-      <c r="BC4"/>
-      <c r="BD4"/>
+      <c r="BC4" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="BD4" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
       <c r="BE4"/>
       <c r="BF4"/>
-      <c r="BG4"/>
-      <c r="BH4"/>
-      <c r="BI4"/>
-      <c r="BJ4"/>
-      <c r="BK4"/>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
       <c r="BL4"/>
       <c r="BM4"/>
       <c r="BN4"/>
       <c r="BO4"/>
-      <c r="BP4"/>
-      <c r="BQ4"/>
-      <c r="BR4"/>
-      <c r="BS4"/>
+      <c r="BP4" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="BQ4" s="3" t="inlineStr">
+        <is>
+          <t>1123454567</t>
+        </is>
+      </c>
+      <c r="BR4" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="BS4" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
       <c r="BT4"/>
-      <c r="BU4"/>
-      <c r="BV4"/>
-      <c r="BW4"/>
+      <c r="BU4" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="BV4" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="BW4" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
       <c r="BX4"/>
       <c r="BY4"/>
       <c r="BZ4"/>
       <c r="CA4"/>
       <c r="CB4"/>
-      <c r="CC4"/>
-      <c r="CD4"/>
-      <c r="CE4"/>
-      <c r="CF4"/>
-      <c r="CG4"/>
-      <c r="CH4"/>
-      <c r="CI4"/>
-      <c r="CJ4"/>
-      <c r="CK4"/>
-      <c r="CL4"/>
+      <c r="CC4" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CD4" s="3" t="inlineStr">
+        <is>
+          <t>ABC123456789</t>
+        </is>
+      </c>
+      <c r="CE4" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CF4" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CG4" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CH4" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CI4" s="3" t="inlineStr">
+        <is>
+          <t>ABC123456789</t>
+        </is>
+      </c>
+      <c r="CJ4" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CK4" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CL4" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="CM4"/>
       <c r="CN4"/>
       <c r="CO4"/>
@@ -2161,16 +2297,34 @@
       <c r="DN4"/>
       <c r="DO4"/>
       <c r="DP4"/>
-      <c r="DQ4"/>
-      <c r="DR4"/>
+      <c r="DQ4" s="4" t="n">
+        <v>43466.0</v>
+      </c>
+      <c r="DR4" s="4" t="n">
+        <v>43466.0</v>
+      </c>
       <c r="DS4"/>
       <c r="DT4"/>
       <c r="DU4"/>
-      <c r="DV4"/>
-      <c r="DW4"/>
-      <c r="DX4"/>
-      <c r="DY4"/>
-      <c r="DZ4"/>
+      <c r="DV4" s="4" t="n">
+        <v>43505.0</v>
+      </c>
+      <c r="DW4" s="1" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="DX4" s="3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="DY4" s="3" t="inlineStr">
+        <is>
+          <t>COVERAGE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="DZ4" s="1" t="n">
+        <v>150.0</v>
+      </c>
       <c r="EA4"/>
       <c r="EB4"/>
       <c r="EC4"/>
@@ -2182,12 +2336,12 @@
       <c r="EI4"/>
       <c r="EJ4" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="EK4" s="3" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="EL4"/>
@@ -2196,10 +2350,10 @@
       <c r="EO4"/>
       <c r="EP4"/>
       <c r="EQ4" s="1" t="n">
-        <v>100.0</v>
+        <v>150.0</v>
       </c>
       <c r="ER4" s="1" t="n">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="ES4" t="n">
         <v>1.0</v>
@@ -2218,7 +2372,7 @@
         <v>43466.0</v>
       </c>
       <c r="FC4" s="1" t="n">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
       <c r="FD4" s="3" t="inlineStr">
         <is>
@@ -2227,11 +2381,11 @@
       </c>
       <c r="FE4" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>45</t>
         </is>
       </c>
       <c r="FF4" s="1" t="n">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
       <c r="FG4"/>
       <c r="FH4"/>
@@ -2261,10 +2415,22 @@
       <c r="GF4"/>
       <c r="GG4"/>
       <c r="GH4"/>
-      <c r="GI4"/>
-      <c r="GJ4"/>
-      <c r="GK4"/>
-      <c r="GL4"/>
+      <c r="GI4" s="1" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="GJ4" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="GK4" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_ACTUAL</t>
+        </is>
+      </c>
+      <c r="GL4" s="1" t="n">
+        <v>80.0</v>
+      </c>
       <c r="GM4"/>
       <c r="GN4"/>
       <c r="GO4"/>
@@ -2283,7 +2449,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02238</t>
+          <t>6a04cbecb80b363c8541f0f8</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2434,12 +2600,12 @@
       <c r="EI5"/>
       <c r="EJ5" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="EK5" s="3" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>85003</t>
         </is>
       </c>
       <c r="EL5"/>
@@ -2448,7 +2614,7 @@
       <c r="EO5"/>
       <c r="EP5"/>
       <c r="EQ5" s="1" t="n">
-        <v>150.0</v>
+        <v>100.0</v>
       </c>
       <c r="ER5" s="1" t="n">
         <v>0.0</v>
@@ -2470,7 +2636,7 @@
         <v>43466.0</v>
       </c>
       <c r="FC5" s="1" t="n">
-        <v>150.0</v>
+        <v>100.0</v>
       </c>
       <c r="FD5" s="3" t="inlineStr">
         <is>
@@ -2479,11 +2645,11 @@
       </c>
       <c r="FE5" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>204</t>
         </is>
       </c>
       <c r="FF5" s="1" t="n">
-        <v>150.0</v>
+        <v>100.0</v>
       </c>
       <c r="FG5"/>
       <c r="FH5"/>
@@ -2535,126 +2701,48 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02265</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>not_covered_inpatient.dat</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>10060875</t>
-        </is>
-      </c>
+          <t>6a04cbecb80b363c8541f0f8</t>
+        </is>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>PATACCT</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>40000.0</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>8000.0</v>
-      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
       <c r="I6"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
+      <c r="J6"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>CLAIMNUMBER</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L6"/>
+      <c r="M6"/>
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
-      <c r="Q6" s="1" t="n">
-        <v>8000.0</v>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
       <c r="T6"/>
-      <c r="U6" s="4" t="n">
-        <v>43693.0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>CK NUMBER 1</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>43704.0</v>
-      </c>
-      <c r="Y6" s="1" t="n">
-        <v>32000.0</v>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="AB6" s="1" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AF6" s="1" t="n">
-        <v>30000.0</v>
-      </c>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
       <c r="AG6"/>
       <c r="AH6"/>
       <c r="AI6"/>
@@ -2668,175 +2756,51 @@
       <c r="AQ6"/>
       <c r="AR6"/>
       <c r="AS6"/>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>ANY PLAN USA</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>1 WALK THIS WAY</t>
-        </is>
-      </c>
+      <c r="AT6"/>
+      <c r="AU6"/>
+      <c r="AV6"/>
+      <c r="AW6"/>
       <c r="AX6"/>
-      <c r="AY6" s="3" t="inlineStr">
-        <is>
-          <t>ANYCITY</t>
-        </is>
-      </c>
-      <c r="AZ6" s="3" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="BA6" s="3" t="inlineStr">
-        <is>
-          <t>45209</t>
-        </is>
-      </c>
+      <c r="AY6"/>
+      <c r="AZ6"/>
+      <c r="BA6"/>
       <c r="BB6"/>
-      <c r="BC6" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="BD6" s="3" t="inlineStr">
-        <is>
-          <t>8661112222</t>
-        </is>
-      </c>
+      <c r="BC6"/>
+      <c r="BD6"/>
       <c r="BE6"/>
       <c r="BF6"/>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>EDI</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="BI6" s="3" t="inlineStr">
-        <is>
-          <t>8002223333</t>
-        </is>
-      </c>
-      <c r="BJ6" s="3" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="BK6" s="3" t="inlineStr">
-        <is>
-          <t>EDI.SUPPORT@ANYPAYER.COM</t>
-        </is>
-      </c>
+      <c r="BG6"/>
+      <c r="BH6"/>
+      <c r="BI6"/>
+      <c r="BJ6"/>
+      <c r="BK6"/>
       <c r="BL6"/>
       <c r="BM6"/>
       <c r="BN6"/>
       <c r="BO6"/>
-      <c r="BP6" s="3" t="inlineStr">
-        <is>
-          <t>NPI</t>
-        </is>
-      </c>
-      <c r="BQ6" s="3" t="inlineStr">
-        <is>
-          <t>1123454567</t>
-        </is>
-      </c>
-      <c r="BR6" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER</t>
-        </is>
-      </c>
-      <c r="BS6" s="3" t="inlineStr">
-        <is>
-          <t>2255 ANY ROAD</t>
-        </is>
-      </c>
+      <c r="BP6"/>
+      <c r="BQ6"/>
+      <c r="BR6"/>
+      <c r="BS6"/>
       <c r="BT6"/>
-      <c r="BU6" s="3" t="inlineStr">
-        <is>
-          <t>ANY CITY</t>
-        </is>
-      </c>
-      <c r="BV6" s="3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="BW6" s="3" t="inlineStr">
-        <is>
-          <t>12211</t>
-        </is>
-      </c>
+      <c r="BU6"/>
+      <c r="BV6"/>
+      <c r="BW6"/>
       <c r="BX6"/>
       <c r="BY6"/>
       <c r="BZ6"/>
       <c r="CA6"/>
       <c r="CB6"/>
-      <c r="CC6" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="CD6" s="3" t="inlineStr">
-        <is>
-          <t>ABC123456789</t>
-        </is>
-      </c>
-      <c r="CE6" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="CF6" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CG6" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="CH6" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="CI6" s="3" t="inlineStr">
-        <is>
-          <t>ABC123456789</t>
-        </is>
-      </c>
-      <c r="CJ6" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="CK6" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CL6" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="CC6"/>
+      <c r="CD6"/>
+      <c r="CE6"/>
+      <c r="CF6"/>
+      <c r="CG6"/>
+      <c r="CH6"/>
+      <c r="CI6"/>
+      <c r="CJ6"/>
+      <c r="CK6"/>
+      <c r="CL6"/>
       <c r="CM6"/>
       <c r="CN6"/>
       <c r="CO6"/>
@@ -2869,67 +2833,47 @@
       <c r="DP6"/>
       <c r="DQ6"/>
       <c r="DR6"/>
-      <c r="DS6" s="4" t="n">
-        <v>43466.0</v>
-      </c>
-      <c r="DT6" s="4" t="n">
-        <v>43470.0</v>
-      </c>
-      <c r="DU6" s="4" t="n">
-        <v>43524.0</v>
-      </c>
-      <c r="DV6" s="4" t="n">
-        <v>43505.0</v>
-      </c>
-      <c r="DW6" s="1" t="n">
-        <v>38000.0</v>
-      </c>
-      <c r="DX6" s="3" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="DY6" s="3" t="inlineStr">
-        <is>
-          <t>COVERAGE_AMOUNT</t>
-        </is>
-      </c>
-      <c r="DZ6" s="1" t="n">
-        <v>38000.0</v>
-      </c>
+      <c r="DS6"/>
+      <c r="DT6"/>
+      <c r="DU6"/>
+      <c r="DV6"/>
+      <c r="DW6"/>
+      <c r="DX6"/>
+      <c r="DY6"/>
+      <c r="DZ6"/>
       <c r="EA6"/>
       <c r="EB6"/>
       <c r="EC6"/>
-      <c r="ED6" s="3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="EE6" s="3" t="inlineStr">
-        <is>
-          <t>COVERED</t>
-        </is>
-      </c>
-      <c r="EF6" t="n">
-        <v>4.0</v>
-      </c>
+      <c r="ED6"/>
+      <c r="EE6"/>
+      <c r="EF6"/>
       <c r="EG6"/>
       <c r="EH6"/>
       <c r="EI6"/>
       <c r="EJ6" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="EK6"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="EK6" s="3" t="inlineStr">
+        <is>
+          <t>36415</t>
+        </is>
+      </c>
       <c r="EL6"/>
       <c r="EM6"/>
       <c r="EN6"/>
       <c r="EO6"/>
       <c r="EP6"/>
-      <c r="EQ6"/>
-      <c r="ER6"/>
-      <c r="ES6"/>
+      <c r="EQ6" s="1" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="ER6" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>1.0</v>
+      </c>
       <c r="ET6"/>
       <c r="EU6"/>
       <c r="EV6"/>
@@ -2937,14 +2881,28 @@
       <c r="EX6"/>
       <c r="EY6"/>
       <c r="EZ6"/>
-      <c r="FA6"/>
-      <c r="FB6"/>
+      <c r="FA6" s="4" t="n">
+        <v>43466.0</v>
+      </c>
+      <c r="FB6" s="4" t="n">
+        <v>43466.0</v>
+      </c>
       <c r="FC6" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="FD6"/>
-      <c r="FE6"/>
-      <c r="FF6"/>
+        <v>150.0</v>
+      </c>
+      <c r="FD6" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FE6" s="3" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="FF6" s="1" t="n">
+        <v>150.0</v>
+      </c>
       <c r="FG6"/>
       <c r="FH6"/>
       <c r="FI6"/>
@@ -2995,7 +2953,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a022be</t>
+          <t>6a04cbecb80b363c8541f125</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3005,17 +2963,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>negotiated_discount.dat</t>
+          <t>not_covered_inpatient.dat</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>10060875</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>7722337</t>
+          <t>PATACCT</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3024,22 +2982,20 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>226.0</v>
+        <v>40000.0</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>132.0</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>10.0</v>
-      </c>
+        <v>8000.0</v>
+      </c>
+      <c r="I7"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>119932404007801</t>
+          <t>CLAIMNUMBER</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -3056,7 +3012,7 @@
       <c r="O7"/>
       <c r="P7"/>
       <c r="Q7" s="1" t="n">
-        <v>132.0</v>
+        <v>8000.0</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
@@ -3068,29 +3024,25 @@
           <t>CHECK</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
+      <c r="T7"/>
       <c r="U7" s="4" t="n">
-        <v>43555.0</v>
+        <v>43693.0</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>CK NUMBER 1</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>1512345678</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="X7" s="4" t="n">
-        <v>43538.0</v>
+        <v>43704.0</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>32405.0</v>
+        <v>32000.0</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -3122,19 +3074,9 @@
         <v>30000.0</v>
       </c>
       <c r="AG7"/>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="AI7" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AJ7" s="1" t="n">
-        <v>259.0</v>
-      </c>
+      <c r="AH7"/>
+      <c r="AI7"/>
+      <c r="AJ7"/>
       <c r="AK7"/>
       <c r="AL7"/>
       <c r="AM7"/>
@@ -3151,40 +3093,36 @@
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>DELTA DENTAL OF ABC</t>
+          <t>ANY PLAN USA</t>
         </is>
       </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>225 MAIN STREET</t>
+          <t>1 WALK THIS WAY</t>
         </is>
       </c>
       <c r="AX7"/>
       <c r="AY7" s="3" t="inlineStr">
         <is>
-          <t>CENTERVILLE</t>
+          <t>ANYCITY</t>
         </is>
       </c>
       <c r="AZ7" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="BA7" s="3" t="inlineStr">
         <is>
-          <t>17111</t>
-        </is>
-      </c>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>JANE DOE</t>
-        </is>
-      </c>
+          <t>45209</t>
+        </is>
+      </c>
+      <c r="BB7"/>
       <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>PHONE</t>
@@ -3192,87 +3130,91 @@
       </c>
       <c r="BD7" s="3" t="inlineStr">
         <is>
-          <t>9005555555</t>
+          <t>8661112222</t>
         </is>
       </c>
       <c r="BE7"/>
       <c r="BF7"/>
-      <c r="BG7"/>
-      <c r="BH7"/>
-      <c r="BI7"/>
-      <c r="BJ7"/>
-      <c r="BK7"/>
-      <c r="BL7" s="3" t="inlineStr">
-        <is>
-          <t>PAYER_IDENTIFICATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="BM7" s="3" t="inlineStr">
-        <is>
-          <t>0101</t>
-        </is>
-      </c>
-      <c r="BN7" s="3" t="inlineStr">
-        <is>
-          <t>HEALTH_INDUSTRY_NUMBER</t>
-        </is>
-      </c>
-      <c r="BO7" s="3" t="inlineStr">
-        <is>
-          <t>0202</t>
-        </is>
-      </c>
+      <c r="BG7" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="BH7" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="BL7"/>
+      <c r="BM7"/>
+      <c r="BN7"/>
+      <c r="BO7"/>
       <c r="BP7" s="3" t="inlineStr">
         <is>
-          <t>EIN</t>
+          <t>NPI</t>
         </is>
       </c>
       <c r="BQ7" s="3" t="inlineStr">
         <is>
-          <t>999994703</t>
+          <t>1123454567</t>
         </is>
       </c>
       <c r="BR7" s="3" t="inlineStr">
         <is>
-          <t>BAN DDS LLC</t>
+          <t>PROVIDER</t>
         </is>
       </c>
       <c r="BS7" s="3" t="inlineStr">
         <is>
-          <t>225 MAIN STREET</t>
+          <t>2255 ANY ROAD</t>
         </is>
       </c>
       <c r="BT7"/>
       <c r="BU7" s="3" t="inlineStr">
         <is>
-          <t>CENTERVILLE</t>
+          <t>ANY CITY</t>
         </is>
       </c>
       <c r="BV7" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="BW7" s="3" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="BX7"/>
-      <c r="BY7" s="3" t="inlineStr">
-        <is>
-          <t>PAYEE_IDENTIFICATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="BZ7" s="3" t="inlineStr">
-        <is>
-          <t>0505</t>
-        </is>
-      </c>
+      <c r="BY7"/>
+      <c r="BZ7"/>
       <c r="CA7"/>
       <c r="CB7"/>
-      <c r="CC7"/>
-      <c r="CD7"/>
+      <c r="CC7" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CD7" s="3" t="inlineStr">
+        <is>
+          <t>ABC123456789</t>
+        </is>
+      </c>
       <c r="CE7" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
@@ -3280,10 +3222,14 @@
       </c>
       <c r="CF7" s="3" t="inlineStr">
         <is>
-          <t>SALLY</t>
-        </is>
-      </c>
-      <c r="CG7"/>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CG7" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="CH7" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -3291,7 +3237,7 @@
       </c>
       <c r="CI7" s="3" t="inlineStr">
         <is>
-          <t>SJD11111</t>
+          <t>ABC123456789</t>
         </is>
       </c>
       <c r="CJ7" s="3" t="inlineStr">
@@ -3301,116 +3247,60 @@
       </c>
       <c r="CK7" s="3" t="inlineStr">
         <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="CL7"/>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CL7" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="CM7"/>
       <c r="CN7"/>
       <c r="CO7"/>
       <c r="CP7"/>
       <c r="CQ7"/>
-      <c r="CR7" s="3" t="inlineStr">
-        <is>
-          <t>NPI</t>
-        </is>
-      </c>
-      <c r="CS7" s="3" t="inlineStr">
-        <is>
-          <t>1811901945</t>
-        </is>
-      </c>
-      <c r="CT7" s="3" t="inlineStr">
-        <is>
-          <t>BAN</t>
-        </is>
-      </c>
-      <c r="CU7" s="3" t="inlineStr">
-        <is>
-          <t>ERIN</t>
-        </is>
-      </c>
+      <c r="CR7"/>
+      <c r="CS7"/>
+      <c r="CT7"/>
+      <c r="CU7"/>
       <c r="CV7"/>
       <c r="CW7"/>
-      <c r="CX7" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_PROVIDER_NUMBER</t>
-        </is>
-      </c>
-      <c r="CY7" s="3" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
+      <c r="CX7"/>
+      <c r="CY7"/>
       <c r="CZ7"/>
       <c r="DA7"/>
-      <c r="DB7" s="3" t="inlineStr">
-        <is>
-          <t>CMS_PLAN_ID</t>
-        </is>
-      </c>
-      <c r="DC7" s="3" t="inlineStr">
-        <is>
-          <t>9876</t>
-        </is>
-      </c>
-      <c r="DD7" s="3" t="inlineStr">
-        <is>
-          <t>ACME INSURANCE</t>
-        </is>
-      </c>
-      <c r="DE7" s="3" t="inlineStr">
-        <is>
-          <t>CMS_PLAN_ID</t>
-        </is>
-      </c>
-      <c r="DF7" s="3" t="inlineStr">
-        <is>
-          <t>8765</t>
-        </is>
-      </c>
-      <c r="DG7" s="3" t="inlineStr">
-        <is>
-          <t>ACME INSURANCE</t>
-        </is>
-      </c>
+      <c r="DB7"/>
+      <c r="DC7"/>
+      <c r="DD7"/>
+      <c r="DE7"/>
+      <c r="DF7"/>
+      <c r="DG7"/>
       <c r="DH7"/>
       <c r="DI7"/>
-      <c r="DJ7" s="3" t="inlineStr">
-        <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="DK7" s="3" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
+      <c r="DJ7"/>
+      <c r="DK7"/>
       <c r="DL7"/>
       <c r="DM7"/>
       <c r="DN7"/>
       <c r="DO7"/>
       <c r="DP7"/>
-      <c r="DQ7" s="4" t="n">
-        <v>43548.0</v>
-      </c>
-      <c r="DR7" s="4" t="n">
-        <v>43549.0</v>
-      </c>
+      <c r="DQ7"/>
+      <c r="DR7"/>
       <c r="DS7" s="4" t="n">
-        <v>44819.0</v>
+        <v>43466.0</v>
       </c>
       <c r="DT7" s="4" t="n">
-        <v>44820.0</v>
+        <v>43470.0</v>
       </c>
       <c r="DU7" s="4" t="n">
-        <v>44835.0</v>
+        <v>43524.0</v>
       </c>
       <c r="DV7" s="4" t="n">
-        <v>44889.0</v>
+        <v>43505.0</v>
       </c>
       <c r="DW7" s="1" t="n">
-        <v>132.0</v>
+        <v>38000.0</v>
       </c>
       <c r="DX7" s="3" t="inlineStr">
         <is>
@@ -3423,21 +3313,11 @@
         </is>
       </c>
       <c r="DZ7" s="1" t="n">
-        <v>132.0</v>
-      </c>
-      <c r="EA7" s="3" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="EB7" s="3" t="inlineStr">
-        <is>
-          <t>DISCOUNT_AMOUNT</t>
-        </is>
-      </c>
-      <c r="EC7" s="1" t="n">
-        <v>100.0</v>
-      </c>
+        <v>38000.0</v>
+      </c>
+      <c r="EA7"/>
+      <c r="EB7"/>
+      <c r="EC7"/>
       <c r="ED7" s="3" t="inlineStr">
         <is>
           <t>CA</t>
@@ -3456,79 +3336,33 @@
       <c r="EI7"/>
       <c r="EJ7" s="3" t="inlineStr">
         <is>
-          <t>A123</t>
-        </is>
-      </c>
-      <c r="EK7" s="3" t="inlineStr">
-        <is>
-          <t>D0120</t>
-        </is>
-      </c>
-      <c r="EL7" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="EM7" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EK7"/>
+      <c r="EL7"/>
+      <c r="EM7"/>
       <c r="EN7"/>
-      <c r="EO7" s="3" t="inlineStr">
-        <is>
-          <t>0222</t>
-        </is>
-      </c>
+      <c r="EO7"/>
       <c r="EP7"/>
-      <c r="EQ7" s="1" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="ER7" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="ES7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="ET7" s="3" t="inlineStr">
-        <is>
-          <t>D0140</t>
-        </is>
-      </c>
-      <c r="EU7" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="EQ7"/>
+      <c r="ER7"/>
+      <c r="ES7"/>
+      <c r="ET7"/>
+      <c r="EU7"/>
       <c r="EV7"/>
       <c r="EW7"/>
       <c r="EX7"/>
       <c r="EY7"/>
-      <c r="EZ7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="FA7" s="4" t="n">
-        <v>43548.0</v>
-      </c>
-      <c r="FB7" s="4" t="n">
-        <v>43548.0</v>
-      </c>
+      <c r="EZ7"/>
+      <c r="FA7"/>
+      <c r="FB7"/>
       <c r="FC7" s="1" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="FD7" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="FE7" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="FF7" s="1" t="n">
-        <v>21.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="FD7"/>
+      <c r="FE7"/>
+      <c r="FF7"/>
       <c r="FG7"/>
       <c r="FH7"/>
       <c r="FI7"/>
@@ -3546,106 +3380,32 @@
       <c r="FU7"/>
       <c r="FV7"/>
       <c r="FW7"/>
-      <c r="FX7" s="3" t="inlineStr">
-        <is>
-          <t>RATE_CODE_NUMBER</t>
-        </is>
-      </c>
-      <c r="FY7" s="3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="FZ7" s="3" t="inlineStr">
-        <is>
-          <t>APG_NUMBER</t>
-        </is>
-      </c>
-      <c r="GA7" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="GB7" s="3" t="inlineStr">
-        <is>
-          <t>AMBULATORY_PAYMENT</t>
-        </is>
-      </c>
-      <c r="GC7" s="3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="GD7" s="3" t="inlineStr">
-        <is>
-          <t>1234"5</t>
-        </is>
-      </c>
-      <c r="GE7" s="3" t="inlineStr">
-        <is>
-          <t>CMS_NPI</t>
-        </is>
-      </c>
-      <c r="GF7" s="3" t="inlineStr">
-        <is>
-          <t>P123</t>
-        </is>
-      </c>
-      <c r="GG7" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_PROVIDER_NUMBER</t>
-        </is>
-      </c>
-      <c r="GH7" s="3" t="inlineStr">
-        <is>
-          <t>P234</t>
-        </is>
-      </c>
-      <c r="GI7" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="GJ7" s="3" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="GK7" s="3" t="inlineStr">
-        <is>
-          <t>ALLOWED_ACTUAL</t>
-        </is>
-      </c>
-      <c r="GL7" s="1" t="n">
-        <v>25.0</v>
-      </c>
+      <c r="FX7"/>
+      <c r="FY7"/>
+      <c r="FZ7"/>
+      <c r="GA7"/>
+      <c r="GB7"/>
+      <c r="GC7"/>
+      <c r="GD7"/>
+      <c r="GE7"/>
+      <c r="GF7"/>
+      <c r="GG7"/>
+      <c r="GH7"/>
+      <c r="GI7"/>
+      <c r="GJ7"/>
+      <c r="GK7"/>
+      <c r="GL7"/>
       <c r="GM7"/>
       <c r="GN7"/>
       <c r="GO7"/>
-      <c r="GP7" s="3" t="inlineStr">
-        <is>
-          <t>ZL</t>
-        </is>
-      </c>
-      <c r="GQ7" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_MEDICAID_CAT_2</t>
-        </is>
-      </c>
-      <c r="GR7" t="n">
-        <v>3.75</v>
-      </c>
+      <c r="GP7"/>
+      <c r="GQ7"/>
+      <c r="GR7"/>
       <c r="GS7"/>
       <c r="GT7"/>
       <c r="GU7"/>
-      <c r="GV7" s="3" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="GW7" s="3" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
+      <c r="GV7"/>
+      <c r="GW7"/>
       <c r="GX7"/>
       <c r="GY7"/>
       <c r="GZ7"/>
@@ -3653,52 +3413,146 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a022be</t>
-        </is>
-      </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
+          <t>6a04cbecb80b363c8541f17e</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>negotiated_discount.dat</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>35681</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
           <t>7722337</t>
         </is>
       </c>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>226.0</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>119932404007801</t>
         </is>
       </c>
-      <c r="L8"/>
-      <c r="M8"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N8"/>
       <c r="O8"/>
       <c r="P8"/>
-      <c r="Q8"/>
-      <c r="R8"/>
-      <c r="S8"/>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8"/>
-      <c r="X8"/>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8"/>
-      <c r="AB8"/>
-      <c r="AC8"/>
-      <c r="AD8"/>
-      <c r="AE8"/>
-      <c r="AF8"/>
+      <c r="Q8" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>43555.0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>1512345678</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>43538.0</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>32405.0</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>30000.0</v>
+      </c>
       <c r="AG8"/>
-      <c r="AH8"/>
-      <c r="AI8"/>
-      <c r="AJ8"/>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>259.0</v>
+      </c>
       <c r="AK8"/>
       <c r="AL8"/>
       <c r="AM8"/>
@@ -3708,17 +3562,57 @@
       <c r="AQ8"/>
       <c r="AR8"/>
       <c r="AS8"/>
-      <c r="AT8"/>
-      <c r="AU8"/>
-      <c r="AV8"/>
-      <c r="AW8"/>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>DELTA DENTAL OF ABC</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
       <c r="AX8"/>
-      <c r="AY8"/>
-      <c r="AZ8"/>
-      <c r="BA8"/>
-      <c r="BB8"/>
-      <c r="BC8"/>
-      <c r="BD8"/>
+      <c r="AY8" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="AZ8" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="BA8" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>JANE DOE</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="BD8" s="3" t="inlineStr">
+        <is>
+          <t>9005555555</t>
+        </is>
+      </c>
       <c r="BE8"/>
       <c r="BF8"/>
       <c r="BG8"/>
@@ -3726,113 +3620,311 @@
       <c r="BI8"/>
       <c r="BJ8"/>
       <c r="BK8"/>
-      <c r="BL8"/>
-      <c r="BM8"/>
-      <c r="BN8"/>
-      <c r="BO8"/>
-      <c r="BP8"/>
-      <c r="BQ8"/>
-      <c r="BR8"/>
-      <c r="BS8"/>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BM8" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="BN8" s="3" t="inlineStr">
+        <is>
+          <t>HEALTH_INDUSTRY_NUMBER</t>
+        </is>
+      </c>
+      <c r="BO8" s="3" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="BP8" s="3" t="inlineStr">
+        <is>
+          <t>EIN</t>
+        </is>
+      </c>
+      <c r="BQ8" s="3" t="inlineStr">
+        <is>
+          <t>999994703</t>
+        </is>
+      </c>
+      <c r="BR8" s="3" t="inlineStr">
+        <is>
+          <t>BAN DDS LLC</t>
+        </is>
+      </c>
+      <c r="BS8" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
       <c r="BT8"/>
-      <c r="BU8"/>
-      <c r="BV8"/>
-      <c r="BW8"/>
+      <c r="BU8" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="BV8" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="BW8" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
       <c r="BX8"/>
-      <c r="BY8"/>
-      <c r="BZ8"/>
+      <c r="BY8" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BZ8" s="3" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
       <c r="CA8"/>
       <c r="CB8"/>
       <c r="CC8"/>
       <c r="CD8"/>
-      <c r="CE8"/>
-      <c r="CF8"/>
+      <c r="CE8" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CF8" s="3" t="inlineStr">
+        <is>
+          <t>SALLY</t>
+        </is>
+      </c>
       <c r="CG8"/>
-      <c r="CH8"/>
-      <c r="CI8"/>
-      <c r="CJ8"/>
-      <c r="CK8"/>
+      <c r="CH8" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CI8" s="3" t="inlineStr">
+        <is>
+          <t>SJD11111</t>
+        </is>
+      </c>
+      <c r="CJ8" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CK8" s="3" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
       <c r="CL8"/>
       <c r="CM8"/>
       <c r="CN8"/>
       <c r="CO8"/>
       <c r="CP8"/>
       <c r="CQ8"/>
-      <c r="CR8"/>
-      <c r="CS8"/>
-      <c r="CT8"/>
-      <c r="CU8"/>
+      <c r="CR8" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="CS8" s="3" t="inlineStr">
+        <is>
+          <t>1811901945</t>
+        </is>
+      </c>
+      <c r="CT8" s="3" t="inlineStr">
+        <is>
+          <t>BAN</t>
+        </is>
+      </c>
+      <c r="CU8" s="3" t="inlineStr">
+        <is>
+          <t>ERIN</t>
+        </is>
+      </c>
       <c r="CV8"/>
       <c r="CW8"/>
-      <c r="CX8"/>
-      <c r="CY8"/>
+      <c r="CX8" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_PROVIDER_NUMBER</t>
+        </is>
+      </c>
+      <c r="CY8" s="3" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
       <c r="CZ8"/>
       <c r="DA8"/>
-      <c r="DB8"/>
-      <c r="DC8"/>
-      <c r="DD8"/>
-      <c r="DE8"/>
-      <c r="DF8"/>
-      <c r="DG8"/>
+      <c r="DB8" s="3" t="inlineStr">
+        <is>
+          <t>CMS_PLAN_ID</t>
+        </is>
+      </c>
+      <c r="DC8" s="3" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="DD8" s="3" t="inlineStr">
+        <is>
+          <t>ACME INSURANCE</t>
+        </is>
+      </c>
+      <c r="DE8" s="3" t="inlineStr">
+        <is>
+          <t>CMS_PLAN_ID</t>
+        </is>
+      </c>
+      <c r="DF8" s="3" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="DG8" s="3" t="inlineStr">
+        <is>
+          <t>ACME INSURANCE</t>
+        </is>
+      </c>
       <c r="DH8"/>
       <c r="DI8"/>
-      <c r="DJ8"/>
-      <c r="DK8"/>
+      <c r="DJ8" s="3" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="DK8" s="3" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
       <c r="DL8"/>
       <c r="DM8"/>
       <c r="DN8"/>
       <c r="DO8"/>
       <c r="DP8"/>
-      <c r="DQ8"/>
-      <c r="DR8"/>
-      <c r="DS8"/>
-      <c r="DT8"/>
-      <c r="DU8"/>
-      <c r="DV8"/>
-      <c r="DW8"/>
-      <c r="DX8"/>
-      <c r="DY8"/>
-      <c r="DZ8"/>
-      <c r="EA8"/>
-      <c r="EB8"/>
-      <c r="EC8"/>
-      <c r="ED8"/>
-      <c r="EE8"/>
-      <c r="EF8"/>
+      <c r="DQ8" s="4" t="n">
+        <v>43548.0</v>
+      </c>
+      <c r="DR8" s="4" t="n">
+        <v>43549.0</v>
+      </c>
+      <c r="DS8" s="4" t="n">
+        <v>44819.0</v>
+      </c>
+      <c r="DT8" s="4" t="n">
+        <v>44820.0</v>
+      </c>
+      <c r="DU8" s="4" t="n">
+        <v>44835.0</v>
+      </c>
+      <c r="DV8" s="4" t="n">
+        <v>44889.0</v>
+      </c>
+      <c r="DW8" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="DX8" s="3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="DY8" s="3" t="inlineStr">
+        <is>
+          <t>COVERAGE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="DZ8" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="EA8" s="3" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="EB8" s="3" t="inlineStr">
+        <is>
+          <t>DISCOUNT_AMOUNT</t>
+        </is>
+      </c>
+      <c r="EC8" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="ED8" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="EE8" s="3" t="inlineStr">
+        <is>
+          <t>COVERED</t>
+        </is>
+      </c>
+      <c r="EF8" t="n">
+        <v>4.0</v>
+      </c>
       <c r="EG8"/>
       <c r="EH8"/>
       <c r="EI8"/>
       <c r="EJ8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>A123</t>
         </is>
       </c>
       <c r="EK8" s="3" t="inlineStr">
         <is>
-          <t>D0220</t>
-        </is>
-      </c>
-      <c r="EL8"/>
-      <c r="EM8"/>
+          <t>D0120</t>
+        </is>
+      </c>
+      <c r="EL8" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="EM8" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="EN8"/>
-      <c r="EO8"/>
+      <c r="EO8" s="3" t="inlineStr">
+        <is>
+          <t>0222</t>
+        </is>
+      </c>
       <c r="EP8"/>
       <c r="EQ8" s="1" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="ER8" s="1" t="n">
         <v>25.0</v>
       </c>
-      <c r="ER8" s="1" t="n">
-        <v>14.0</v>
-      </c>
       <c r="ES8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="ET8"/>
-      <c r="EU8"/>
+        <v>3.1</v>
+      </c>
+      <c r="ET8" s="3" t="inlineStr">
+        <is>
+          <t>D0140</t>
+        </is>
+      </c>
+      <c r="EU8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="EV8"/>
       <c r="EW8"/>
       <c r="EX8"/>
       <c r="EY8"/>
-      <c r="EZ8"/>
+      <c r="EZ8" t="n">
+        <v>3.5</v>
+      </c>
       <c r="FA8" s="4" t="n">
         <v>43548.0</v>
       </c>
@@ -3840,7 +3932,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC8" s="1" t="n">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="FD8" s="3" t="inlineStr">
         <is>
@@ -3853,7 +3945,7 @@
         </is>
       </c>
       <c r="FF8" s="1" t="n">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="FG8"/>
       <c r="FH8"/>
@@ -3872,19 +3964,63 @@
       <c r="FU8"/>
       <c r="FV8"/>
       <c r="FW8"/>
-      <c r="FX8"/>
-      <c r="FY8"/>
-      <c r="FZ8"/>
-      <c r="GA8"/>
-      <c r="GB8"/>
-      <c r="GC8"/>
-      <c r="GD8"/>
-      <c r="GE8"/>
-      <c r="GF8"/>
-      <c r="GG8"/>
-      <c r="GH8"/>
+      <c r="FX8" s="3" t="inlineStr">
+        <is>
+          <t>RATE_CODE_NUMBER</t>
+        </is>
+      </c>
+      <c r="FY8" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="FZ8" s="3" t="inlineStr">
+        <is>
+          <t>APG_NUMBER</t>
+        </is>
+      </c>
+      <c r="GA8" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="GB8" s="3" t="inlineStr">
+        <is>
+          <t>AMBULATORY_PAYMENT</t>
+        </is>
+      </c>
+      <c r="GC8" s="3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="GD8" s="3" t="inlineStr">
+        <is>
+          <t>1234"5</t>
+        </is>
+      </c>
+      <c r="GE8" s="3" t="inlineStr">
+        <is>
+          <t>CMS_NPI</t>
+        </is>
+      </c>
+      <c r="GF8" s="3" t="inlineStr">
+        <is>
+          <t>P123</t>
+        </is>
+      </c>
+      <c r="GG8" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_PROVIDER_NUMBER</t>
+        </is>
+      </c>
+      <c r="GH8" s="3" t="inlineStr">
+        <is>
+          <t>P234</t>
+        </is>
+      </c>
       <c r="GI8" s="1" t="n">
-        <v>14.0</v>
+        <v>25.0</v>
       </c>
       <c r="GJ8" s="3" t="inlineStr">
         <is>
@@ -3897,19 +4033,37 @@
         </is>
       </c>
       <c r="GL8" s="1" t="n">
-        <v>14.0</v>
+        <v>25.0</v>
       </c>
       <c r="GM8"/>
       <c r="GN8"/>
       <c r="GO8"/>
-      <c r="GP8"/>
-      <c r="GQ8"/>
-      <c r="GR8"/>
+      <c r="GP8" s="3" t="inlineStr">
+        <is>
+          <t>ZL</t>
+        </is>
+      </c>
+      <c r="GQ8" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_MEDICAID_CAT_2</t>
+        </is>
+      </c>
+      <c r="GR8" t="n">
+        <v>3.75</v>
+      </c>
       <c r="GS8"/>
       <c r="GT8"/>
       <c r="GU8"/>
-      <c r="GV8"/>
-      <c r="GW8"/>
+      <c r="GV8" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="GW8" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
       <c r="GX8"/>
       <c r="GY8"/>
       <c r="GZ8"/>
@@ -3917,7 +4071,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a022be</t>
+          <t>6a04cbecb80b363c8541f17e</t>
         </is>
       </c>
       <c r="B9"/>
@@ -4068,12 +4222,12 @@
       <c r="EI9"/>
       <c r="EJ9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="EK9" s="3" t="inlineStr">
         <is>
-          <t>D0230</t>
+          <t>D0220</t>
         </is>
       </c>
       <c r="EL9"/>
@@ -4082,10 +4236,10 @@
       <c r="EO9"/>
       <c r="EP9"/>
       <c r="EQ9" s="1" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="ER9" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="ES9" t="n">
         <v>1.0</v>
@@ -4104,7 +4258,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC9" s="1" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="FD9" s="3" t="inlineStr">
         <is>
@@ -4117,7 +4271,7 @@
         </is>
       </c>
       <c r="FF9" s="1" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="FG9"/>
       <c r="FH9"/>
@@ -4148,7 +4302,7 @@
       <c r="GG9"/>
       <c r="GH9"/>
       <c r="GI9" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="GJ9" s="3" t="inlineStr">
         <is>
@@ -4161,7 +4315,7 @@
         </is>
       </c>
       <c r="GL9" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="GM9"/>
       <c r="GN9"/>
@@ -4181,7 +4335,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a022be</t>
+          <t>6a04cbecb80b363c8541f17e</t>
         </is>
       </c>
       <c r="B10"/>
@@ -4332,12 +4486,12 @@
       <c r="EI10"/>
       <c r="EJ10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EK10" s="3" t="inlineStr">
         <is>
-          <t>D0274</t>
+          <t>D0230</t>
         </is>
       </c>
       <c r="EL10"/>
@@ -4346,10 +4500,10 @@
       <c r="EO10"/>
       <c r="EP10"/>
       <c r="EQ10" s="1" t="n">
-        <v>60.0</v>
+        <v>22.0</v>
       </c>
       <c r="ER10" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="ES10" t="n">
         <v>1.0</v>
@@ -4368,7 +4522,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC10" s="1" t="n">
-        <v>26.0</v>
+        <v>12.0</v>
       </c>
       <c r="FD10" s="3" t="inlineStr">
         <is>
@@ -4381,7 +4535,7 @@
         </is>
       </c>
       <c r="FF10" s="1" t="n">
-        <v>26.0</v>
+        <v>12.0</v>
       </c>
       <c r="FG10"/>
       <c r="FH10"/>
@@ -4412,7 +4566,7 @@
       <c r="GG10"/>
       <c r="GH10"/>
       <c r="GI10" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="GJ10" s="3" t="inlineStr">
         <is>
@@ -4425,7 +4579,7 @@
         </is>
       </c>
       <c r="GL10" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="GM10"/>
       <c r="GN10"/>
@@ -4445,7 +4599,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a022be</t>
+          <t>6a04cbecb80b363c8541f17e</t>
         </is>
       </c>
       <c r="B11"/>
@@ -4596,12 +4750,12 @@
       <c r="EI11"/>
       <c r="EJ11" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="EK11" s="3" t="inlineStr">
         <is>
-          <t>D1110</t>
+          <t>D0274</t>
         </is>
       </c>
       <c r="EL11"/>
@@ -4610,10 +4764,10 @@
       <c r="EO11"/>
       <c r="EP11"/>
       <c r="EQ11" s="1" t="n">
-        <v>73.0</v>
+        <v>60.0</v>
       </c>
       <c r="ER11" s="1" t="n">
-        <v>49.0</v>
+        <v>34.0</v>
       </c>
       <c r="ES11" t="n">
         <v>1.0</v>
@@ -4629,10 +4783,10 @@
         <v>43548.0</v>
       </c>
       <c r="FB11" s="4" t="n">
-        <v>43549.0</v>
+        <v>43548.0</v>
       </c>
       <c r="FC11" s="1" t="n">
-        <v>76.0</v>
+        <v>26.0</v>
       </c>
       <c r="FD11" s="3" t="inlineStr">
         <is>
@@ -4645,36 +4799,16 @@
         </is>
       </c>
       <c r="FF11" s="1" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="FG11"/>
-      <c r="FH11" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="FI11" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="FJ11" s="1" t="n">
-        <v>25.0</v>
-      </c>
+      <c r="FH11"/>
+      <c r="FI11"/>
+      <c r="FJ11"/>
       <c r="FK11"/>
-      <c r="FL11" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="FM11" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="FN11" s="1" t="n">
-        <v>27.0</v>
-      </c>
+      <c r="FL11"/>
+      <c r="FM11"/>
+      <c r="FN11"/>
       <c r="FO11"/>
       <c r="FP11"/>
       <c r="FQ11"/>
@@ -4696,7 +4830,7 @@
       <c r="GG11"/>
       <c r="GH11"/>
       <c r="GI11" s="1" t="n">
-        <v>49.0</v>
+        <v>34.0</v>
       </c>
       <c r="GJ11" s="3" t="inlineStr">
         <is>
@@ -4709,21 +4843,11 @@
         </is>
       </c>
       <c r="GL11" s="1" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="GM11" s="3" t="inlineStr">
-        <is>
-          <t>KH</t>
-        </is>
-      </c>
-      <c r="GN11" s="3" t="inlineStr">
-        <is>
-          <t>DEDUCTION</t>
-        </is>
-      </c>
-      <c r="GO11" s="1" t="n">
-        <v>50.0</v>
-      </c>
+        <v>34.0</v>
+      </c>
+      <c r="GM11"/>
+      <c r="GN11"/>
+      <c r="GO11"/>
       <c r="GP11"/>
       <c r="GQ11"/>
       <c r="GR11"/>
@@ -4739,103 +4863,41 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a022f0</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>dollars_data_separate.dat</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>112233</t>
-        </is>
-      </c>
+          <t>6a04cbecb80b363c8541f17e</t>
+        </is>
+      </c>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>5554555444</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>800.0</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>7722337</t>
+        </is>
+      </c>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>94060555410000</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>119932404007801</t>
+        </is>
+      </c>
+      <c r="L12"/>
+      <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12"/>
-      <c r="Q12" s="1" t="n">
-        <v>1100.0</v>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>ACH</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>144444</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>43540.0</v>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>71700666555</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t>1935665544</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="n">
-        <v>43538.0</v>
-      </c>
-      <c r="Y12" s="1" t="n">
-        <v>300.0</v>
-      </c>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
       <c r="Z12"/>
       <c r="AA12"/>
       <c r="AB12"/>
@@ -4856,67 +4918,19 @@
       <c r="AQ12"/>
       <c r="AR12"/>
       <c r="AS12"/>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>1935665544</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>RUSHMORE LIFE</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>10 SOUTH AVENUET</t>
-        </is>
-      </c>
+      <c r="AT12"/>
+      <c r="AU12"/>
+      <c r="AV12"/>
+      <c r="AW12"/>
       <c r="AX12"/>
-      <c r="AY12" s="3" t="inlineStr">
-        <is>
-          <t>RAPID CITY</t>
-        </is>
-      </c>
-      <c r="AZ12" s="3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="BA12" s="3" t="inlineStr">
-        <is>
-          <t>55111</t>
-        </is>
-      </c>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>JOHN WAYNE</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr">
-        <is>
-          <t>8005551212</t>
-        </is>
-      </c>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
+      <c r="AY12"/>
+      <c r="AZ12"/>
+      <c r="BA12"/>
+      <c r="BB12"/>
+      <c r="BC12"/>
+      <c r="BD12"/>
+      <c r="BE12"/>
+      <c r="BF12"/>
       <c r="BG12"/>
       <c r="BH12"/>
       <c r="BI12"/>
@@ -4926,21 +4940,9 @@
       <c r="BM12"/>
       <c r="BN12"/>
       <c r="BO12"/>
-      <c r="BP12" s="3" t="inlineStr">
-        <is>
-          <t>NPI</t>
-        </is>
-      </c>
-      <c r="BQ12" s="3" t="inlineStr">
-        <is>
-          <t>5544667733</t>
-        </is>
-      </c>
-      <c r="BR12" s="3" t="inlineStr">
-        <is>
-          <t>ACME MEDICAL CENTER</t>
-        </is>
-      </c>
+      <c r="BP12"/>
+      <c r="BQ12"/>
+      <c r="BR12"/>
       <c r="BS12"/>
       <c r="BT12"/>
       <c r="BU12"/>
@@ -4951,47 +4953,15 @@
       <c r="BZ12"/>
       <c r="CA12"/>
       <c r="CB12"/>
-      <c r="CC12" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="CD12" s="3" t="inlineStr">
-        <is>
-          <t>33344555510</t>
-        </is>
-      </c>
-      <c r="CE12" s="3" t="inlineStr">
-        <is>
-          <t>BUDD</t>
-        </is>
-      </c>
-      <c r="CF12" s="3" t="inlineStr">
-        <is>
-          <t>WILLIAM</t>
-        </is>
-      </c>
+      <c r="CC12"/>
+      <c r="CD12"/>
+      <c r="CE12"/>
+      <c r="CF12"/>
       <c r="CG12"/>
-      <c r="CH12" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="CI12" s="3" t="inlineStr">
-        <is>
-          <t>33344555510</t>
-        </is>
-      </c>
-      <c r="CJ12" s="3" t="inlineStr">
-        <is>
-          <t>BUDD</t>
-        </is>
-      </c>
-      <c r="CK12" s="3" t="inlineStr">
-        <is>
-          <t>WILLIAM</t>
-        </is>
-      </c>
+      <c r="CH12"/>
+      <c r="CI12"/>
+      <c r="CJ12"/>
+      <c r="CK12"/>
       <c r="CL12"/>
       <c r="CM12"/>
       <c r="CN12"/>
@@ -5023,32 +4993,16 @@
       <c r="DN12"/>
       <c r="DO12"/>
       <c r="DP12"/>
-      <c r="DQ12" s="4" t="n">
-        <v>44986.0</v>
-      </c>
-      <c r="DR12" s="4" t="n">
-        <v>44986.0</v>
-      </c>
+      <c r="DQ12"/>
+      <c r="DR12"/>
       <c r="DS12"/>
       <c r="DT12"/>
       <c r="DU12"/>
       <c r="DV12"/>
-      <c r="DW12" s="1" t="n">
-        <v>800.0</v>
-      </c>
-      <c r="DX12" s="3" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="DY12" s="3" t="inlineStr">
-        <is>
-          <t>COVERAGE_AMOUNT</t>
-        </is>
-      </c>
-      <c r="DZ12" s="1" t="n">
-        <v>800.0</v>
-      </c>
+      <c r="DW12"/>
+      <c r="DX12"/>
+      <c r="DY12"/>
+      <c r="DZ12"/>
       <c r="EA12"/>
       <c r="EB12"/>
       <c r="EC12"/>
@@ -5060,12 +5014,12 @@
       <c r="EI12"/>
       <c r="EJ12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EK12" s="3" t="inlineStr">
         <is>
-          <t>99211</t>
+          <t>D1110</t>
         </is>
       </c>
       <c r="EL12"/>
@@ -5074,10 +5028,10 @@
       <c r="EO12"/>
       <c r="EP12"/>
       <c r="EQ12" s="1" t="n">
-        <v>800.0</v>
+        <v>73.0</v>
       </c>
       <c r="ER12" s="1" t="n">
-        <v>500.0</v>
+        <v>49.0</v>
       </c>
       <c r="ES12" t="n">
         <v>1.0</v>
@@ -5090,35 +5044,55 @@
       <c r="EY12"/>
       <c r="EZ12"/>
       <c r="FA12" s="4" t="n">
-        <v>44986.0</v>
+        <v>43548.0</v>
       </c>
       <c r="FB12" s="4" t="n">
-        <v>44986.0</v>
+        <v>43549.0</v>
       </c>
       <c r="FC12" s="1" t="n">
-        <v>300.0</v>
+        <v>76.0</v>
       </c>
       <c r="FD12" s="3" t="inlineStr">
         <is>
-          <t>PATIENT_RESPONSIBILITY</t>
+          <t>CONTRACTUAL</t>
         </is>
       </c>
       <c r="FE12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>131</t>
         </is>
       </c>
       <c r="FF12" s="1" t="n">
-        <v>300.0</v>
+        <v>24.0</v>
       </c>
       <c r="FG12"/>
-      <c r="FH12"/>
-      <c r="FI12"/>
-      <c r="FJ12"/>
+      <c r="FH12" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FI12" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FJ12" s="1" t="n">
+        <v>25.0</v>
+      </c>
       <c r="FK12"/>
-      <c r="FL12"/>
-      <c r="FM12"/>
-      <c r="FN12"/>
+      <c r="FL12" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="FM12" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="FN12" s="1" t="n">
+        <v>27.0</v>
+      </c>
       <c r="FO12"/>
       <c r="FP12"/>
       <c r="FQ12"/>
@@ -5140,7 +5114,7 @@
       <c r="GG12"/>
       <c r="GH12"/>
       <c r="GI12" s="1" t="n">
-        <v>800.0</v>
+        <v>49.0</v>
       </c>
       <c r="GJ12" s="3" t="inlineStr">
         <is>
@@ -5153,11 +5127,21 @@
         </is>
       </c>
       <c r="GL12" s="1" t="n">
-        <v>800.0</v>
-      </c>
-      <c r="GM12"/>
-      <c r="GN12"/>
-      <c r="GO12"/>
+        <v>49.0</v>
+      </c>
+      <c r="GM12" s="3" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="GN12" s="3" t="inlineStr">
+        <is>
+          <t>DEDUCTION</t>
+        </is>
+      </c>
+      <c r="GO12" s="1" t="n">
+        <v>50.0</v>
+      </c>
       <c r="GP12"/>
       <c r="GQ12"/>
       <c r="GR12"/>
@@ -5173,7 +5157,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a022f1</t>
+          <t>6a04cbecb80b363c8541f1b0</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -5193,7 +5177,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>8765432112</t>
+          <t>5554555444</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -5202,13 +5186,13 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1200.0</v>
+        <v>800.0</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>600.0</v>
+        <v>500.0</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>600.0</v>
+        <v>300.0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -5217,7 +5201,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>9407779923000</t>
+          <t>94060555410000</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5268,7 +5252,7 @@
         <v>43538.0</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>600.0</v>
+        <v>300.0</v>
       </c>
       <c r="Z13"/>
       <c r="AA13"/>
@@ -5392,17 +5376,17 @@
       </c>
       <c r="CD13" s="3" t="inlineStr">
         <is>
-          <t>44455666610</t>
+          <t>33344555510</t>
         </is>
       </c>
       <c r="CE13" s="3" t="inlineStr">
         <is>
-          <t>SETTLE</t>
+          <t>BUDD</t>
         </is>
       </c>
       <c r="CF13" s="3" t="inlineStr">
         <is>
-          <t>SUSAN</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="CG13"/>
@@ -5413,17 +5397,17 @@
       </c>
       <c r="CI13" s="3" t="inlineStr">
         <is>
-          <t>44455666610</t>
+          <t>33344555510</t>
         </is>
       </c>
       <c r="CJ13" s="3" t="inlineStr">
         <is>
-          <t>SETTLE</t>
+          <t>BUDD</t>
         </is>
       </c>
       <c r="CK13" s="3" t="inlineStr">
         <is>
-          <t>SUSAN</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="CL13"/>
@@ -5458,17 +5442,17 @@
       <c r="DO13"/>
       <c r="DP13"/>
       <c r="DQ13" s="4" t="n">
-        <v>44995.0</v>
+        <v>44986.0</v>
       </c>
       <c r="DR13" s="4" t="n">
-        <v>44995.0</v>
+        <v>44986.0</v>
       </c>
       <c r="DS13"/>
       <c r="DT13"/>
       <c r="DU13"/>
       <c r="DV13"/>
       <c r="DW13" s="1" t="n">
-        <v>1200.0</v>
+        <v>800.0</v>
       </c>
       <c r="DX13" s="3" t="inlineStr">
         <is>
@@ -5481,7 +5465,7 @@
         </is>
       </c>
       <c r="DZ13" s="1" t="n">
-        <v>1200.0</v>
+        <v>800.0</v>
       </c>
       <c r="EA13"/>
       <c r="EB13"/>
@@ -5499,7 +5483,7 @@
       </c>
       <c r="EK13" s="3" t="inlineStr">
         <is>
-          <t>93555</t>
+          <t>99211</t>
         </is>
       </c>
       <c r="EL13"/>
@@ -5508,10 +5492,10 @@
       <c r="EO13"/>
       <c r="EP13"/>
       <c r="EQ13" s="1" t="n">
-        <v>1200.0</v>
+        <v>800.0</v>
       </c>
       <c r="ER13" s="1" t="n">
-        <v>600.0</v>
+        <v>500.0</v>
       </c>
       <c r="ES13" t="n">
         <v>1.0</v>
@@ -5524,13 +5508,13 @@
       <c r="EY13"/>
       <c r="EZ13"/>
       <c r="FA13" s="4" t="n">
-        <v>44995.0</v>
+        <v>44986.0</v>
       </c>
       <c r="FB13" s="4" t="n">
-        <v>44995.0</v>
+        <v>44986.0</v>
       </c>
       <c r="FC13" s="1" t="n">
-        <v>600.0</v>
+        <v>300.0</v>
       </c>
       <c r="FD13" s="3" t="inlineStr">
         <is>
@@ -5543,7 +5527,7 @@
         </is>
       </c>
       <c r="FF13" s="1" t="n">
-        <v>600.0</v>
+        <v>300.0</v>
       </c>
       <c r="FG13"/>
       <c r="FH13"/>
@@ -5574,7 +5558,7 @@
       <c r="GG13"/>
       <c r="GH13"/>
       <c r="GI13" s="1" t="n">
-        <v>1200.0</v>
+        <v>800.0</v>
       </c>
       <c r="GJ13" s="3" t="inlineStr">
         <is>
@@ -5587,7 +5571,7 @@
         </is>
       </c>
       <c r="GL13" s="1" t="n">
-        <v>1200.0</v>
+        <v>800.0</v>
       </c>
       <c r="GM13"/>
       <c r="GN13"/>
@@ -5607,7 +5591,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0231f</t>
+          <t>6a04cbecb80b363c8541f1b1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -5617,39 +5601,41 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>835-denial.dat</t>
+          <t>dollars_data_separate.dat</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>10060875</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>PATACCT</t>
+          <t>8765432112</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>DENIED</t>
+          <t>PRIMARY</t>
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>150.0</v>
+        <v>1200.0</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I14"/>
+        <v>600.0</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>600.0</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>CLAIMNUMBER</t>
+          <t>9407779923000</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5666,7 +5652,7 @@
       <c r="O14"/>
       <c r="P14"/>
       <c r="Q14" s="1" t="n">
-        <v>0.0</v>
+        <v>1100.0</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
@@ -5675,28 +5661,32 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>NON_PAYMENT</t>
-        </is>
-      </c>
-      <c r="T14"/>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>144444</t>
+        </is>
+      </c>
       <c r="U14" s="4" t="n">
-        <v>43693.0</v>
+        <v>43540.0</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>TRACE123</t>
+          <t>71700666555</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>1935665544</t>
         </is>
       </c>
       <c r="X14" s="4" t="n">
-        <v>43704.0</v>
+        <v>43538.0</v>
       </c>
       <c r="Y14" s="1" t="n">
-        <v>150.0</v>
+        <v>600.0</v>
       </c>
       <c r="Z14"/>
       <c r="AA14"/>
@@ -5725,36 +5715,40 @@
       </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>1935665544</t>
         </is>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>ANY PLAN USA</t>
+          <t>RUSHMORE LIFE</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>1 WALK THIS WAY</t>
+          <t>10 SOUTH AVENUET</t>
         </is>
       </c>
       <c r="AX14"/>
       <c r="AY14" s="3" t="inlineStr">
         <is>
-          <t>ANYCITY</t>
+          <t>RAPID CITY</t>
         </is>
       </c>
       <c r="AZ14" s="3" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="BA14" s="3" t="inlineStr">
         <is>
-          <t>45209</t>
-        </is>
-      </c>
-      <c r="BB14"/>
+          <t>55111</t>
+        </is>
+      </c>
+      <c r="BB14" s="3" t="inlineStr">
+        <is>
+          <t>JOHN WAYNE</t>
+        </is>
+      </c>
       <c r="BC14" s="3" t="inlineStr">
         <is>
           <t>PHONE</t>
@@ -5762,36 +5756,24 @@
       </c>
       <c r="BD14" s="3" t="inlineStr">
         <is>
-          <t>8661112222</t>
-        </is>
-      </c>
-      <c r="BE14"/>
-      <c r="BF14"/>
-      <c r="BG14" s="3" t="inlineStr">
-        <is>
-          <t>EDI</t>
-        </is>
-      </c>
-      <c r="BH14" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="BI14" s="3" t="inlineStr">
-        <is>
-          <t>8002223333</t>
-        </is>
-      </c>
-      <c r="BJ14" s="3" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="BK14" s="3" t="inlineStr">
-        <is>
-          <t>EDI.SUPPORT@ANYPAYER.COM</t>
-        </is>
-      </c>
+          <t>8005551212</t>
+        </is>
+      </c>
+      <c r="BE14" s="3" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="BF14" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="BG14"/>
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
+      <c r="BK14"/>
       <c r="BL14"/>
       <c r="BM14"/>
       <c r="BN14"/>
@@ -5803,35 +5785,19 @@
       </c>
       <c r="BQ14" s="3" t="inlineStr">
         <is>
-          <t>1123454567</t>
+          <t>5544667733</t>
         </is>
       </c>
       <c r="BR14" s="3" t="inlineStr">
         <is>
-          <t>PROVIDER</t>
-        </is>
-      </c>
-      <c r="BS14" s="3" t="inlineStr">
-        <is>
-          <t>2255 ANY ROAD</t>
-        </is>
-      </c>
+          <t>ACME MEDICAL CENTER</t>
+        </is>
+      </c>
+      <c r="BS14"/>
       <c r="BT14"/>
-      <c r="BU14" s="3" t="inlineStr">
-        <is>
-          <t>ANY CITY</t>
-        </is>
-      </c>
-      <c r="BV14" s="3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="BW14" s="3" t="inlineStr">
-        <is>
-          <t>12211</t>
-        </is>
-      </c>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
       <c r="BX14"/>
       <c r="BY14"/>
       <c r="BZ14"/>
@@ -5844,24 +5810,20 @@
       </c>
       <c r="CD14" s="3" t="inlineStr">
         <is>
-          <t>ABC123456789</t>
+          <t>44455666610</t>
         </is>
       </c>
       <c r="CE14" s="3" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>SETTLE</t>
         </is>
       </c>
       <c r="CF14" s="3" t="inlineStr">
         <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CG14" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>SUSAN</t>
+        </is>
+      </c>
+      <c r="CG14"/>
       <c r="CH14" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -5869,24 +5831,20 @@
       </c>
       <c r="CI14" s="3" t="inlineStr">
         <is>
-          <t>ABC123456789</t>
+          <t>44455666610</t>
         </is>
       </c>
       <c r="CJ14" s="3" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>SETTLE</t>
         </is>
       </c>
       <c r="CK14" s="3" t="inlineStr">
         <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CL14" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>SUSAN</t>
+        </is>
+      </c>
+      <c r="CL14"/>
       <c r="CM14"/>
       <c r="CN14"/>
       <c r="CO14"/>
@@ -5918,19 +5876,17 @@
       <c r="DO14"/>
       <c r="DP14"/>
       <c r="DQ14" s="4" t="n">
-        <v>43466.0</v>
+        <v>44995.0</v>
       </c>
       <c r="DR14" s="4" t="n">
-        <v>43466.0</v>
+        <v>44995.0</v>
       </c>
       <c r="DS14"/>
       <c r="DT14"/>
       <c r="DU14"/>
-      <c r="DV14" s="4" t="n">
-        <v>43505.0</v>
-      </c>
+      <c r="DV14"/>
       <c r="DW14" s="1" t="n">
-        <v>150.0</v>
+        <v>1200.0</v>
       </c>
       <c r="DX14" s="3" t="inlineStr">
         <is>
@@ -5943,7 +5899,7 @@
         </is>
       </c>
       <c r="DZ14" s="1" t="n">
-        <v>150.0</v>
+        <v>1200.0</v>
       </c>
       <c r="EA14"/>
       <c r="EB14"/>
@@ -5956,12 +5912,12 @@
       <c r="EI14"/>
       <c r="EJ14" s="3" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1</t>
         </is>
       </c>
       <c r="EK14" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>93555</t>
         </is>
       </c>
       <c r="EL14"/>
@@ -5970,10 +5926,10 @@
       <c r="EO14"/>
       <c r="EP14"/>
       <c r="EQ14" s="1" t="n">
-        <v>150.0</v>
+        <v>1200.0</v>
       </c>
       <c r="ER14" s="1" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
       <c r="ES14" t="n">
         <v>1.0</v>
@@ -5986,26 +5942,26 @@
       <c r="EY14"/>
       <c r="EZ14"/>
       <c r="FA14" s="4" t="n">
-        <v>43466.0</v>
+        <v>44995.0</v>
       </c>
       <c r="FB14" s="4" t="n">
-        <v>43466.0</v>
+        <v>44995.0</v>
       </c>
       <c r="FC14" s="1" t="n">
-        <v>150.0</v>
+        <v>600.0</v>
       </c>
       <c r="FD14" s="3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PATIENT_RESPONSIBILITY</t>
         </is>
       </c>
       <c r="FE14" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FF14" s="1" t="n">
-        <v>150.0</v>
+        <v>600.0</v>
       </c>
       <c r="FG14"/>
       <c r="FH14"/>
@@ -6031,22 +5987,26 @@
       <c r="GB14"/>
       <c r="GC14"/>
       <c r="GD14"/>
-      <c r="GE14" s="3" t="inlineStr">
-        <is>
-          <t>CMS_NPI</t>
-        </is>
-      </c>
-      <c r="GF14" s="3" t="inlineStr">
-        <is>
-          <t>99123</t>
-        </is>
-      </c>
+      <c r="GE14"/>
+      <c r="GF14"/>
       <c r="GG14"/>
       <c r="GH14"/>
-      <c r="GI14"/>
-      <c r="GJ14"/>
-      <c r="GK14"/>
-      <c r="GL14"/>
+      <c r="GI14" s="1" t="n">
+        <v>1200.0</v>
+      </c>
+      <c r="GJ14" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="GK14" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_ACTUAL</t>
+        </is>
+      </c>
+      <c r="GL14" s="1" t="n">
+        <v>1200.0</v>
+      </c>
       <c r="GM14"/>
       <c r="GN14"/>
       <c r="GO14"/>
@@ -6056,11 +6016,7 @@
       <c r="GS14"/>
       <c r="GT14"/>
       <c r="GU14"/>
-      <c r="GV14" s="3" t="inlineStr">
-        <is>
-          <t>M143</t>
-        </is>
-      </c>
+      <c r="GV14"/>
       <c r="GW14"/>
       <c r="GX14"/>
       <c r="GY14"/>
@@ -6069,7 +6025,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0238c</t>
+          <t>6a04cbecb80b363c8541f1df</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6079,41 +6035,39 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>835-all-fields.dat</t>
+          <t>835-denial.dat</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>10060875</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>7722337</t>
+          <t>PATACCT</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>DENIED</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>226.0</v>
+        <v>150.0</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>132.0</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>10.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="I15"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>119932404007801</t>
+          <t>CLAIMNUMBER</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -6126,19 +6080,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
       <c r="Q15" s="1" t="n">
-        <v>132.0</v>
+        <v>0.0</v>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
@@ -6147,76 +6093,40 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ACH</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>2200008888</t>
-        </is>
-      </c>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="T15"/>
       <c r="U15" s="4" t="n">
-        <v>45756.0</v>
+        <v>43693.0</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>882509401093167</t>
+          <t>TRACE123</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>106609999</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="X15" s="4" t="n">
-        <v>43538.0</v>
+        <v>43704.0</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>32405.0</v>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="AB15" s="1" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AF15" s="1" t="n">
-        <v>30000.0</v>
-      </c>
+        <v>150.0</v>
+      </c>
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
       <c r="AG15"/>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="AI15" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AJ15" s="1" t="n">
-        <v>259.0</v>
-      </c>
+      <c r="AH15"/>
+      <c r="AI15"/>
+      <c r="AJ15"/>
       <c r="AK15"/>
       <c r="AL15"/>
       <c r="AM15"/>
@@ -6233,40 +6143,36 @@
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>DELTA DENTAL OF ABC</t>
+          <t>ANY PLAN USA</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>225 MAIN STREET</t>
+          <t>1 WALK THIS WAY</t>
         </is>
       </c>
       <c r="AX15"/>
       <c r="AY15" s="3" t="inlineStr">
         <is>
-          <t>CENTERVILLE</t>
+          <t>ANYCITY</t>
         </is>
       </c>
       <c r="AZ15" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="BA15" s="3" t="inlineStr">
         <is>
-          <t>17111</t>
-        </is>
-      </c>
-      <c r="BB15" s="3" t="inlineStr">
-        <is>
-          <t>JANE DOE</t>
-        </is>
-      </c>
+          <t>45209</t>
+        </is>
+      </c>
+      <c r="BB15"/>
       <c r="BC15" s="3" t="inlineStr">
         <is>
           <t>PHONE</t>
@@ -6274,103 +6180,91 @@
       </c>
       <c r="BD15" s="3" t="inlineStr">
         <is>
-          <t>9005555555</t>
-        </is>
-      </c>
-      <c r="BE15" s="3" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="BF15" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="BG15"/>
+          <t>8661112222</t>
+        </is>
+      </c>
+      <c r="BE15"/>
+      <c r="BF15"/>
+      <c r="BG15" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
       <c r="BH15" s="3" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="BI15" s="3" t="inlineStr">
         <is>
-          <t>myplan.com/policies</t>
-        </is>
-      </c>
-      <c r="BJ15"/>
-      <c r="BK15"/>
-      <c r="BL15" s="3" t="inlineStr">
-        <is>
-          <t>PAYER_IDENTIFICATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="BM15" s="3" t="inlineStr">
-        <is>
-          <t>0101</t>
-        </is>
-      </c>
-      <c r="BN15" s="3" t="inlineStr">
-        <is>
-          <t>HEALTH_INDUSTRY_NUMBER</t>
-        </is>
-      </c>
-      <c r="BO15" s="3" t="inlineStr">
-        <is>
-          <t>0202</t>
-        </is>
-      </c>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="BJ15" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="BL15"/>
+      <c r="BM15"/>
+      <c r="BN15"/>
+      <c r="BO15"/>
       <c r="BP15" s="3" t="inlineStr">
         <is>
-          <t>EIN</t>
+          <t>NPI</t>
         </is>
       </c>
       <c r="BQ15" s="3" t="inlineStr">
         <is>
-          <t>999994703</t>
+          <t>1123454567</t>
         </is>
       </c>
       <c r="BR15" s="3" t="inlineStr">
         <is>
-          <t>BAN DDS LLC</t>
+          <t>PROVIDER</t>
         </is>
       </c>
       <c r="BS15" s="3" t="inlineStr">
         <is>
-          <t>225 MAIN STREET</t>
+          <t>2255 ANY ROAD</t>
         </is>
       </c>
       <c r="BT15"/>
       <c r="BU15" s="3" t="inlineStr">
         <is>
-          <t>CENTERVILLE</t>
+          <t>ANY CITY</t>
         </is>
       </c>
       <c r="BV15" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="BW15" s="3" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="BX15"/>
-      <c r="BY15" s="3" t="inlineStr">
-        <is>
-          <t>PAYEE_IDENTIFICATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="BZ15" s="3" t="inlineStr">
-        <is>
-          <t>0505</t>
-        </is>
-      </c>
+      <c r="BY15"/>
+      <c r="BZ15"/>
       <c r="CA15"/>
       <c r="CB15"/>
-      <c r="CC15"/>
-      <c r="CD15"/>
+      <c r="CC15" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CD15" s="3" t="inlineStr">
+        <is>
+          <t>ABC123456789</t>
+        </is>
+      </c>
       <c r="CE15" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
@@ -6378,10 +6272,14 @@
       </c>
       <c r="CF15" s="3" t="inlineStr">
         <is>
-          <t>SALLY</t>
-        </is>
-      </c>
-      <c r="CG15"/>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CG15" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="CH15" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -6389,7 +6287,7 @@
       </c>
       <c r="CI15" s="3" t="inlineStr">
         <is>
-          <t>SJD11111</t>
+          <t>ABC123456789</t>
         </is>
       </c>
       <c r="CJ15" s="3" t="inlineStr">
@@ -6399,136 +6297,58 @@
       </c>
       <c r="CK15" s="3" t="inlineStr">
         <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="CL15"/>
-      <c r="CM15" s="3" t="inlineStr">
-        <is>
-          <t>INSURED_CHANGED_ID</t>
-        </is>
-      </c>
-      <c r="CN15" s="3" t="inlineStr">
-        <is>
-          <t>SJD999</t>
-        </is>
-      </c>
-      <c r="CO15" s="3" t="inlineStr">
-        <is>
-          <t>Due</t>
-        </is>
-      </c>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CL15" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CM15"/>
+      <c r="CN15"/>
+      <c r="CO15"/>
       <c r="CP15"/>
       <c r="CQ15"/>
-      <c r="CR15" s="3" t="inlineStr">
-        <is>
-          <t>NPI</t>
-        </is>
-      </c>
-      <c r="CS15" s="3" t="inlineStr">
-        <is>
-          <t>1811901945</t>
-        </is>
-      </c>
-      <c r="CT15" s="3" t="inlineStr">
-        <is>
-          <t>BAN</t>
-        </is>
-      </c>
-      <c r="CU15" s="3" t="inlineStr">
-        <is>
-          <t>ERIN</t>
-        </is>
-      </c>
+      <c r="CR15"/>
+      <c r="CS15"/>
+      <c r="CT15"/>
+      <c r="CU15"/>
       <c r="CV15"/>
       <c r="CW15"/>
-      <c r="CX15" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_PROVIDER_NUMBER</t>
-        </is>
-      </c>
-      <c r="CY15" s="3" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="CZ15" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="DA15" s="3" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="DB15" s="3" t="inlineStr">
-        <is>
-          <t>CMS_PLAN_ID</t>
-        </is>
-      </c>
-      <c r="DC15" s="3" t="inlineStr">
-        <is>
-          <t>9876</t>
-        </is>
-      </c>
-      <c r="DD15" s="3" t="inlineStr">
-        <is>
-          <t>ACME INSURANCE</t>
-        </is>
-      </c>
-      <c r="DE15" s="3" t="inlineStr">
-        <is>
-          <t>CMS_PLAN_ID</t>
-        </is>
-      </c>
-      <c r="DF15" s="3" t="inlineStr">
-        <is>
-          <t>8765</t>
-        </is>
-      </c>
-      <c r="DG15" s="3" t="inlineStr">
-        <is>
-          <t>ACME INSURANCE</t>
-        </is>
-      </c>
+      <c r="CX15"/>
+      <c r="CY15"/>
+      <c r="CZ15"/>
+      <c r="DA15"/>
+      <c r="DB15"/>
+      <c r="DC15"/>
+      <c r="DD15"/>
+      <c r="DE15"/>
+      <c r="DF15"/>
+      <c r="DG15"/>
       <c r="DH15"/>
       <c r="DI15"/>
-      <c r="DJ15" s="3" t="inlineStr">
-        <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="DK15" s="3" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
+      <c r="DJ15"/>
+      <c r="DK15"/>
       <c r="DL15"/>
       <c r="DM15"/>
       <c r="DN15"/>
       <c r="DO15"/>
       <c r="DP15"/>
       <c r="DQ15" s="4" t="n">
-        <v>43548.0</v>
+        <v>43466.0</v>
       </c>
       <c r="DR15" s="4" t="n">
-        <v>43549.0</v>
-      </c>
-      <c r="DS15" s="4" t="n">
-        <v>44819.0</v>
-      </c>
-      <c r="DT15" s="4" t="n">
-        <v>44820.0</v>
-      </c>
-      <c r="DU15" s="4" t="n">
-        <v>44835.0</v>
-      </c>
+        <v>43466.0</v>
+      </c>
+      <c r="DS15"/>
+      <c r="DT15"/>
+      <c r="DU15"/>
       <c r="DV15" s="4" t="n">
-        <v>44889.0</v>
+        <v>43505.0</v>
       </c>
       <c r="DW15" s="1" t="n">
-        <v>132.0</v>
+        <v>150.0</v>
       </c>
       <c r="DX15" s="3" t="inlineStr">
         <is>
@@ -6541,111 +6361,69 @@
         </is>
       </c>
       <c r="DZ15" s="1" t="n">
-        <v>132.0</v>
-      </c>
-      <c r="EA15" s="3" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="EB15" s="3" t="inlineStr">
-        <is>
-          <t>DISCOUNT_AMOUNT</t>
-        </is>
-      </c>
-      <c r="EC15" s="1" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="ED15" s="3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="EE15" s="3" t="inlineStr">
-        <is>
-          <t>COVERED</t>
-        </is>
-      </c>
-      <c r="EF15" t="n">
-        <v>4.0</v>
-      </c>
+        <v>150.0</v>
+      </c>
+      <c r="EA15"/>
+      <c r="EB15"/>
+      <c r="EC15"/>
+      <c r="ED15"/>
+      <c r="EE15"/>
+      <c r="EF15"/>
       <c r="EG15"/>
       <c r="EH15"/>
       <c r="EI15"/>
       <c r="EJ15" s="3" t="inlineStr">
         <is>
-          <t>A123</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="EK15" s="3" t="inlineStr">
         <is>
-          <t>D0120</t>
-        </is>
-      </c>
-      <c r="EL15" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="EM15" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>99213</t>
+        </is>
+      </c>
+      <c r="EL15"/>
+      <c r="EM15"/>
       <c r="EN15"/>
-      <c r="EO15" s="3" t="inlineStr">
-        <is>
-          <t>0022</t>
-        </is>
-      </c>
+      <c r="EO15"/>
       <c r="EP15"/>
       <c r="EQ15" s="1" t="n">
-        <v>46.0</v>
+        <v>150.0</v>
       </c>
       <c r="ER15" s="1" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="ES15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="ET15" s="3" t="inlineStr">
-        <is>
-          <t>D0140</t>
-        </is>
-      </c>
-      <c r="EU15" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="ET15"/>
+      <c r="EU15"/>
       <c r="EV15"/>
       <c r="EW15"/>
       <c r="EX15"/>
       <c r="EY15"/>
-      <c r="EZ15" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="EZ15"/>
       <c r="FA15" s="4" t="n">
-        <v>43548.0</v>
+        <v>43466.0</v>
       </c>
       <c r="FB15" s="4" t="n">
-        <v>43548.0</v>
+        <v>43466.0</v>
       </c>
       <c r="FC15" s="1" t="n">
-        <v>21.0</v>
+        <v>150.0</v>
       </c>
       <c r="FD15" s="3" t="inlineStr">
         <is>
-          <t>CONTRACTUAL</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="FE15" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>252</t>
         </is>
       </c>
       <c r="FF15" s="1" t="n">
-        <v>21.0</v>
+        <v>150.0</v>
       </c>
       <c r="FG15"/>
       <c r="FH15"/>
@@ -6664,41 +6442,13 @@
       <c r="FU15"/>
       <c r="FV15"/>
       <c r="FW15"/>
-      <c r="FX15" s="3" t="inlineStr">
-        <is>
-          <t>RATE_CODE_NUMBER</t>
-        </is>
-      </c>
-      <c r="FY15" s="3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="FZ15" s="3" t="inlineStr">
-        <is>
-          <t>APG_NUMBER</t>
-        </is>
-      </c>
-      <c r="GA15" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="GB15" s="3" t="inlineStr">
-        <is>
-          <t>AMBULATORY_PAYMENT</t>
-        </is>
-      </c>
-      <c r="GC15" s="3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="GD15" s="3" t="inlineStr">
-        <is>
-          <t>1234"5</t>
-        </is>
-      </c>
+      <c r="FX15"/>
+      <c r="FY15"/>
+      <c r="FZ15"/>
+      <c r="GA15"/>
+      <c r="GB15"/>
+      <c r="GC15"/>
+      <c r="GD15"/>
       <c r="GE15" s="3" t="inlineStr">
         <is>
           <t>CMS_NPI</t>
@@ -6706,64 +6456,30 @@
       </c>
       <c r="GF15" s="3" t="inlineStr">
         <is>
-          <t>P123</t>
-        </is>
-      </c>
-      <c r="GG15" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_PROVIDER_NUMBER</t>
-        </is>
-      </c>
-      <c r="GH15" s="3" t="inlineStr">
-        <is>
-          <t>P234</t>
-        </is>
-      </c>
-      <c r="GI15" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="GJ15" s="3" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="GK15" s="3" t="inlineStr">
-        <is>
-          <t>ALLOWED_ACTUAL</t>
-        </is>
-      </c>
-      <c r="GL15" s="1" t="n">
-        <v>25.0</v>
-      </c>
+          <t>99123</t>
+        </is>
+      </c>
+      <c r="GG15"/>
+      <c r="GH15"/>
+      <c r="GI15"/>
+      <c r="GJ15"/>
+      <c r="GK15"/>
+      <c r="GL15"/>
       <c r="GM15"/>
       <c r="GN15"/>
       <c r="GO15"/>
-      <c r="GP15" s="3" t="inlineStr">
-        <is>
-          <t>ZL</t>
-        </is>
-      </c>
-      <c r="GQ15" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_MEDICAID_CAT_2</t>
-        </is>
-      </c>
-      <c r="GR15" t="n">
-        <v>3.75</v>
-      </c>
+      <c r="GP15"/>
+      <c r="GQ15"/>
+      <c r="GR15"/>
       <c r="GS15"/>
       <c r="GT15"/>
       <c r="GU15"/>
       <c r="GV15" s="3" t="inlineStr">
         <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="GW15" s="3" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
+          <t>M143</t>
+        </is>
+      </c>
+      <c r="GW15"/>
       <c r="GX15"/>
       <c r="GY15"/>
       <c r="GZ15"/>
@@ -6771,52 +6487,154 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0238c</t>
-        </is>
-      </c>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
+          <t>6a04cbecb80b363c8541f24c</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>835-all-fields.dat</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>35681</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>7722337</t>
         </is>
       </c>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>226.0</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>119932404007801</t>
         </is>
       </c>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-      <c r="P16"/>
-      <c r="Q16"/>
-      <c r="R16"/>
-      <c r="S16"/>
-      <c r="T16"/>
-      <c r="U16"/>
-      <c r="V16"/>
-      <c r="W16"/>
-      <c r="X16"/>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16"/>
-      <c r="AB16"/>
-      <c r="AC16"/>
-      <c r="AD16"/>
-      <c r="AE16"/>
-      <c r="AF16"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>2200008888</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>45756.0</v>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>882509401093167</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>106609999</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>43538.0</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>32405.0</v>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>30000.0</v>
+      </c>
       <c r="AG16"/>
-      <c r="AH16"/>
-      <c r="AI16"/>
-      <c r="AJ16"/>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>259.0</v>
+      </c>
       <c r="AK16"/>
       <c r="AL16"/>
       <c r="AM16"/>
@@ -6826,131 +6644,405 @@
       <c r="AQ16"/>
       <c r="AR16"/>
       <c r="AS16"/>
-      <c r="AT16"/>
-      <c r="AU16"/>
-      <c r="AV16"/>
-      <c r="AW16"/>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>DELTA DENTAL OF ABC</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
       <c r="AX16"/>
-      <c r="AY16"/>
-      <c r="AZ16"/>
-      <c r="BA16"/>
-      <c r="BB16"/>
-      <c r="BC16"/>
-      <c r="BD16"/>
-      <c r="BE16"/>
-      <c r="BF16"/>
+      <c r="AY16" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="AZ16" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="BA16" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
+      <c r="BB16" s="3" t="inlineStr">
+        <is>
+          <t>JANE DOE</t>
+        </is>
+      </c>
+      <c r="BC16" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="BD16" s="3" t="inlineStr">
+        <is>
+          <t>9005555555</t>
+        </is>
+      </c>
+      <c r="BE16" s="3" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="BF16" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
       <c r="BG16"/>
-      <c r="BH16"/>
-      <c r="BI16"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
+        <is>
+          <t>myplan.com/policies</t>
+        </is>
+      </c>
       <c r="BJ16"/>
       <c r="BK16"/>
-      <c r="BL16"/>
-      <c r="BM16"/>
-      <c r="BN16"/>
-      <c r="BO16"/>
-      <c r="BP16"/>
-      <c r="BQ16"/>
-      <c r="BR16"/>
-      <c r="BS16"/>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BM16" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="BN16" s="3" t="inlineStr">
+        <is>
+          <t>HEALTH_INDUSTRY_NUMBER</t>
+        </is>
+      </c>
+      <c r="BO16" s="3" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="BP16" s="3" t="inlineStr">
+        <is>
+          <t>EIN</t>
+        </is>
+      </c>
+      <c r="BQ16" s="3" t="inlineStr">
+        <is>
+          <t>999994703</t>
+        </is>
+      </c>
+      <c r="BR16" s="3" t="inlineStr">
+        <is>
+          <t>BAN DDS LLC</t>
+        </is>
+      </c>
+      <c r="BS16" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
       <c r="BT16"/>
-      <c r="BU16"/>
-      <c r="BV16"/>
-      <c r="BW16"/>
+      <c r="BU16" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="BV16" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="BW16" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
       <c r="BX16"/>
-      <c r="BY16"/>
-      <c r="BZ16"/>
+      <c r="BY16" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BZ16" s="3" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
       <c r="CA16"/>
       <c r="CB16"/>
       <c r="CC16"/>
       <c r="CD16"/>
-      <c r="CE16"/>
-      <c r="CF16"/>
+      <c r="CE16" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CF16" s="3" t="inlineStr">
+        <is>
+          <t>SALLY</t>
+        </is>
+      </c>
       <c r="CG16"/>
-      <c r="CH16"/>
-      <c r="CI16"/>
-      <c r="CJ16"/>
-      <c r="CK16"/>
+      <c r="CH16" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CI16" s="3" t="inlineStr">
+        <is>
+          <t>SJD11111</t>
+        </is>
+      </c>
+      <c r="CJ16" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CK16" s="3" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
       <c r="CL16"/>
-      <c r="CM16"/>
-      <c r="CN16"/>
-      <c r="CO16"/>
+      <c r="CM16" s="3" t="inlineStr">
+        <is>
+          <t>INSURED_CHANGED_ID</t>
+        </is>
+      </c>
+      <c r="CN16" s="3" t="inlineStr">
+        <is>
+          <t>SJD999</t>
+        </is>
+      </c>
+      <c r="CO16" s="3" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
       <c r="CP16"/>
       <c r="CQ16"/>
-      <c r="CR16"/>
-      <c r="CS16"/>
-      <c r="CT16"/>
-      <c r="CU16"/>
+      <c r="CR16" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="CS16" s="3" t="inlineStr">
+        <is>
+          <t>1811901945</t>
+        </is>
+      </c>
+      <c r="CT16" s="3" t="inlineStr">
+        <is>
+          <t>BAN</t>
+        </is>
+      </c>
+      <c r="CU16" s="3" t="inlineStr">
+        <is>
+          <t>ERIN</t>
+        </is>
+      </c>
       <c r="CV16"/>
       <c r="CW16"/>
-      <c r="CX16"/>
-      <c r="CY16"/>
-      <c r="CZ16"/>
-      <c r="DA16"/>
-      <c r="DB16"/>
-      <c r="DC16"/>
-      <c r="DD16"/>
-      <c r="DE16"/>
-      <c r="DF16"/>
-      <c r="DG16"/>
+      <c r="CX16" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_PROVIDER_NUMBER</t>
+        </is>
+      </c>
+      <c r="CY16" s="3" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="CZ16" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="DA16" s="3" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="DB16" s="3" t="inlineStr">
+        <is>
+          <t>CMS_PLAN_ID</t>
+        </is>
+      </c>
+      <c r="DC16" s="3" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="DD16" s="3" t="inlineStr">
+        <is>
+          <t>ACME INSURANCE</t>
+        </is>
+      </c>
+      <c r="DE16" s="3" t="inlineStr">
+        <is>
+          <t>CMS_PLAN_ID</t>
+        </is>
+      </c>
+      <c r="DF16" s="3" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="DG16" s="3" t="inlineStr">
+        <is>
+          <t>ACME INSURANCE</t>
+        </is>
+      </c>
       <c r="DH16"/>
       <c r="DI16"/>
-      <c r="DJ16"/>
-      <c r="DK16"/>
+      <c r="DJ16" s="3" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="DK16" s="3" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
       <c r="DL16"/>
       <c r="DM16"/>
       <c r="DN16"/>
       <c r="DO16"/>
       <c r="DP16"/>
-      <c r="DQ16"/>
-      <c r="DR16"/>
-      <c r="DS16"/>
-      <c r="DT16"/>
-      <c r="DU16"/>
-      <c r="DV16"/>
-      <c r="DW16"/>
-      <c r="DX16"/>
-      <c r="DY16"/>
-      <c r="DZ16"/>
-      <c r="EA16"/>
-      <c r="EB16"/>
-      <c r="EC16"/>
-      <c r="ED16"/>
-      <c r="EE16"/>
-      <c r="EF16"/>
+      <c r="DQ16" s="4" t="n">
+        <v>43548.0</v>
+      </c>
+      <c r="DR16" s="4" t="n">
+        <v>43549.0</v>
+      </c>
+      <c r="DS16" s="4" t="n">
+        <v>44819.0</v>
+      </c>
+      <c r="DT16" s="4" t="n">
+        <v>44820.0</v>
+      </c>
+      <c r="DU16" s="4" t="n">
+        <v>44835.0</v>
+      </c>
+      <c r="DV16" s="4" t="n">
+        <v>44889.0</v>
+      </c>
+      <c r="DW16" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="DX16" s="3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="DY16" s="3" t="inlineStr">
+        <is>
+          <t>COVERAGE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="DZ16" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="EA16" s="3" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="EB16" s="3" t="inlineStr">
+        <is>
+          <t>DISCOUNT_AMOUNT</t>
+        </is>
+      </c>
+      <c r="EC16" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="ED16" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="EE16" s="3" t="inlineStr">
+        <is>
+          <t>COVERED</t>
+        </is>
+      </c>
+      <c r="EF16" t="n">
+        <v>4.0</v>
+      </c>
       <c r="EG16"/>
       <c r="EH16"/>
       <c r="EI16"/>
       <c r="EJ16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>A123</t>
         </is>
       </c>
       <c r="EK16" s="3" t="inlineStr">
         <is>
-          <t>D0220</t>
-        </is>
-      </c>
-      <c r="EL16"/>
-      <c r="EM16"/>
+          <t>D0120</t>
+        </is>
+      </c>
+      <c r="EL16" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="EM16" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="EN16"/>
-      <c r="EO16"/>
+      <c r="EO16" s="3" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
       <c r="EP16"/>
       <c r="EQ16" s="1" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="ER16" s="1" t="n">
         <v>25.0</v>
       </c>
-      <c r="ER16" s="1" t="n">
-        <v>14.0</v>
-      </c>
       <c r="ES16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="ET16"/>
-      <c r="EU16"/>
+        <v>3.1</v>
+      </c>
+      <c r="ET16" s="3" t="inlineStr">
+        <is>
+          <t>D0140</t>
+        </is>
+      </c>
+      <c r="EU16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="EV16"/>
       <c r="EW16"/>
       <c r="EX16"/>
       <c r="EY16"/>
-      <c r="EZ16"/>
+      <c r="EZ16" t="n">
+        <v>3.5</v>
+      </c>
       <c r="FA16" s="4" t="n">
         <v>43548.0</v>
       </c>
@@ -6958,7 +7050,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC16" s="1" t="n">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="FD16" s="3" t="inlineStr">
         <is>
@@ -6971,7 +7063,7 @@
         </is>
       </c>
       <c r="FF16" s="1" t="n">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="FG16"/>
       <c r="FH16"/>
@@ -6990,19 +7082,63 @@
       <c r="FU16"/>
       <c r="FV16"/>
       <c r="FW16"/>
-      <c r="FX16"/>
-      <c r="FY16"/>
-      <c r="FZ16"/>
-      <c r="GA16"/>
-      <c r="GB16"/>
-      <c r="GC16"/>
-      <c r="GD16"/>
-      <c r="GE16"/>
-      <c r="GF16"/>
-      <c r="GG16"/>
-      <c r="GH16"/>
+      <c r="FX16" s="3" t="inlineStr">
+        <is>
+          <t>RATE_CODE_NUMBER</t>
+        </is>
+      </c>
+      <c r="FY16" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="FZ16" s="3" t="inlineStr">
+        <is>
+          <t>APG_NUMBER</t>
+        </is>
+      </c>
+      <c r="GA16" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="GB16" s="3" t="inlineStr">
+        <is>
+          <t>AMBULATORY_PAYMENT</t>
+        </is>
+      </c>
+      <c r="GC16" s="3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="GD16" s="3" t="inlineStr">
+        <is>
+          <t>1234"5</t>
+        </is>
+      </c>
+      <c r="GE16" s="3" t="inlineStr">
+        <is>
+          <t>CMS_NPI</t>
+        </is>
+      </c>
+      <c r="GF16" s="3" t="inlineStr">
+        <is>
+          <t>P123</t>
+        </is>
+      </c>
+      <c r="GG16" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_PROVIDER_NUMBER</t>
+        </is>
+      </c>
+      <c r="GH16" s="3" t="inlineStr">
+        <is>
+          <t>P234</t>
+        </is>
+      </c>
       <c r="GI16" s="1" t="n">
-        <v>14.0</v>
+        <v>25.0</v>
       </c>
       <c r="GJ16" s="3" t="inlineStr">
         <is>
@@ -7015,19 +7151,37 @@
         </is>
       </c>
       <c r="GL16" s="1" t="n">
-        <v>14.0</v>
+        <v>25.0</v>
       </c>
       <c r="GM16"/>
       <c r="GN16"/>
       <c r="GO16"/>
-      <c r="GP16"/>
-      <c r="GQ16"/>
-      <c r="GR16"/>
+      <c r="GP16" s="3" t="inlineStr">
+        <is>
+          <t>ZL</t>
+        </is>
+      </c>
+      <c r="GQ16" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_MEDICAID_CAT_2</t>
+        </is>
+      </c>
+      <c r="GR16" t="n">
+        <v>3.75</v>
+      </c>
       <c r="GS16"/>
       <c r="GT16"/>
       <c r="GU16"/>
-      <c r="GV16"/>
-      <c r="GW16"/>
+      <c r="GV16" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="GW16" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
       <c r="GX16"/>
       <c r="GY16"/>
       <c r="GZ16"/>
@@ -7035,7 +7189,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0238c</t>
+          <t>6a04cbecb80b363c8541f24c</t>
         </is>
       </c>
       <c r="B17"/>
@@ -7186,12 +7340,12 @@
       <c r="EI17"/>
       <c r="EJ17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="EK17" s="3" t="inlineStr">
         <is>
-          <t>D0230</t>
+          <t>D0220</t>
         </is>
       </c>
       <c r="EL17"/>
@@ -7200,10 +7354,10 @@
       <c r="EO17"/>
       <c r="EP17"/>
       <c r="EQ17" s="1" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="ER17" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="ES17" t="n">
         <v>1.0</v>
@@ -7222,7 +7376,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC17" s="1" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="FD17" s="3" t="inlineStr">
         <is>
@@ -7235,7 +7389,7 @@
         </is>
       </c>
       <c r="FF17" s="1" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="FG17"/>
       <c r="FH17"/>
@@ -7266,7 +7420,7 @@
       <c r="GG17"/>
       <c r="GH17"/>
       <c r="GI17" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="GJ17" s="3" t="inlineStr">
         <is>
@@ -7279,7 +7433,7 @@
         </is>
       </c>
       <c r="GL17" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="GM17"/>
       <c r="GN17"/>
@@ -7299,7 +7453,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0238c</t>
+          <t>6a04cbecb80b363c8541f24c</t>
         </is>
       </c>
       <c r="B18"/>
@@ -7450,12 +7604,12 @@
       <c r="EI18"/>
       <c r="EJ18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EK18" s="3" t="inlineStr">
         <is>
-          <t>D0274</t>
+          <t>D0230</t>
         </is>
       </c>
       <c r="EL18"/>
@@ -7464,10 +7618,10 @@
       <c r="EO18"/>
       <c r="EP18"/>
       <c r="EQ18" s="1" t="n">
-        <v>60.0</v>
+        <v>22.0</v>
       </c>
       <c r="ER18" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="ES18" t="n">
         <v>1.0</v>
@@ -7486,7 +7640,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC18" s="1" t="n">
-        <v>26.0</v>
+        <v>12.0</v>
       </c>
       <c r="FD18" s="3" t="inlineStr">
         <is>
@@ -7499,7 +7653,7 @@
         </is>
       </c>
       <c r="FF18" s="1" t="n">
-        <v>26.0</v>
+        <v>12.0</v>
       </c>
       <c r="FG18"/>
       <c r="FH18"/>
@@ -7530,7 +7684,7 @@
       <c r="GG18"/>
       <c r="GH18"/>
       <c r="GI18" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="GJ18" s="3" t="inlineStr">
         <is>
@@ -7543,7 +7697,7 @@
         </is>
       </c>
       <c r="GL18" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="GM18"/>
       <c r="GN18"/>
@@ -7563,7 +7717,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0238c</t>
+          <t>6a04cbecb80b363c8541f24c</t>
         </is>
       </c>
       <c r="B19"/>
@@ -7714,24 +7868,24 @@
       <c r="EI19"/>
       <c r="EJ19" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="EK19"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="EK19" s="3" t="inlineStr">
+        <is>
+          <t>D0274</t>
+        </is>
+      </c>
       <c r="EL19"/>
       <c r="EM19"/>
       <c r="EN19"/>
-      <c r="EO19" s="3" t="inlineStr">
-        <is>
-          <t>0022</t>
-        </is>
-      </c>
+      <c r="EO19"/>
       <c r="EP19"/>
       <c r="EQ19" s="1" t="n">
-        <v>99.0</v>
+        <v>60.0</v>
       </c>
       <c r="ER19" s="1" t="n">
-        <v>59.0</v>
+        <v>34.0</v>
       </c>
       <c r="ES19" t="n">
         <v>1.0</v>
@@ -7740,15 +7894,9 @@
       <c r="EU19"/>
       <c r="EV19"/>
       <c r="EW19"/>
-      <c r="EX19" s="3" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="EX19"/>
       <c r="EY19"/>
-      <c r="EZ19" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="EZ19"/>
       <c r="FA19" s="4" t="n">
         <v>43548.0</v>
       </c>
@@ -7756,11 +7904,21 @@
         <v>43548.0</v>
       </c>
       <c r="FC19" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="FD19"/>
-      <c r="FE19"/>
-      <c r="FF19"/>
+        <v>26.0</v>
+      </c>
+      <c r="FD19" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FE19" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="FF19" s="1" t="n">
+        <v>26.0</v>
+      </c>
       <c r="FG19"/>
       <c r="FH19"/>
       <c r="FI19"/>
@@ -7789,10 +7947,22 @@
       <c r="GF19"/>
       <c r="GG19"/>
       <c r="GH19"/>
-      <c r="GI19"/>
-      <c r="GJ19"/>
-      <c r="GK19"/>
-      <c r="GL19"/>
+      <c r="GI19" s="1" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="GJ19" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="GK19" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_ACTUAL</t>
+        </is>
+      </c>
+      <c r="GL19" s="1" t="n">
+        <v>34.0</v>
+      </c>
       <c r="GM19"/>
       <c r="GN19"/>
       <c r="GO19"/>
@@ -7811,7 +7981,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0238c</t>
+          <t>6a04cbecb80b363c8541f24c</t>
         </is>
       </c>
       <c r="B20"/>
@@ -7962,24 +8132,24 @@
       <c r="EI20"/>
       <c r="EJ20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="EK20" s="3" t="inlineStr">
-        <is>
-          <t>D1110</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EK20"/>
       <c r="EL20"/>
       <c r="EM20"/>
       <c r="EN20"/>
-      <c r="EO20"/>
+      <c r="EO20" s="3" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
       <c r="EP20"/>
       <c r="EQ20" s="1" t="n">
-        <v>73.0</v>
+        <v>99.0</v>
       </c>
       <c r="ER20" s="1" t="n">
-        <v>49.0</v>
+        <v>59.0</v>
       </c>
       <c r="ES20" t="n">
         <v>1.0</v>
@@ -7988,59 +8158,35 @@
       <c r="EU20"/>
       <c r="EV20"/>
       <c r="EW20"/>
-      <c r="EX20"/>
+      <c r="EX20" s="3" t="inlineStr">
+        <is>
+          <t>0023</t>
+        </is>
+      </c>
       <c r="EY20"/>
-      <c r="EZ20"/>
+      <c r="EZ20" t="n">
+        <v>2.0</v>
+      </c>
       <c r="FA20" s="4" t="n">
         <v>43548.0</v>
       </c>
       <c r="FB20" s="4" t="n">
-        <v>43549.0</v>
+        <v>43548.0</v>
       </c>
       <c r="FC20" s="1" t="n">
-        <v>76.0</v>
-      </c>
-      <c r="FD20" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="FE20" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="FF20" s="1" t="n">
-        <v>24.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="FD20"/>
+      <c r="FE20"/>
+      <c r="FF20"/>
       <c r="FG20"/>
-      <c r="FH20" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="FI20" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="FJ20" s="1" t="n">
-        <v>25.0</v>
-      </c>
+      <c r="FH20"/>
+      <c r="FI20"/>
+      <c r="FJ20"/>
       <c r="FK20"/>
-      <c r="FL20" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="FM20" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="FN20" s="1" t="n">
-        <v>27.0</v>
-      </c>
+      <c r="FL20"/>
+      <c r="FM20"/>
+      <c r="FN20"/>
       <c r="FO20"/>
       <c r="FP20"/>
       <c r="FQ20"/>
@@ -8061,35 +8207,13 @@
       <c r="GF20"/>
       <c r="GG20"/>
       <c r="GH20"/>
-      <c r="GI20" s="1" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="GJ20" s="3" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="GK20" s="3" t="inlineStr">
-        <is>
-          <t>ALLOWED_ACTUAL</t>
-        </is>
-      </c>
-      <c r="GL20" s="1" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="GM20" s="3" t="inlineStr">
-        <is>
-          <t>KH</t>
-        </is>
-      </c>
-      <c r="GN20" s="3" t="inlineStr">
-        <is>
-          <t>DEDUCTION</t>
-        </is>
-      </c>
-      <c r="GO20" s="1" t="n">
-        <v>50.0</v>
-      </c>
+      <c r="GI20"/>
+      <c r="GJ20"/>
+      <c r="GK20"/>
+      <c r="GL20"/>
+      <c r="GM20"/>
+      <c r="GN20"/>
+      <c r="GO20"/>
       <c r="GP20"/>
       <c r="GQ20"/>
       <c r="GR20"/>
@@ -8105,7 +8229,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a0238c</t>
+          <t>6a04cbecb80b363c8541f24c</t>
         </is>
       </c>
       <c r="B21"/>
@@ -8256,61 +8380,85 @@
       <c r="EI21"/>
       <c r="EJ21" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="EK21"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="EK21" s="3" t="inlineStr">
+        <is>
+          <t>D1110</t>
+        </is>
+      </c>
       <c r="EL21"/>
       <c r="EM21"/>
       <c r="EN21"/>
       <c r="EO21"/>
-      <c r="EP21" s="3" t="inlineStr">
-        <is>
-          <t>00002143481</t>
-        </is>
-      </c>
+      <c r="EP21"/>
       <c r="EQ21" s="1" t="n">
-        <v>60.0</v>
+        <v>73.0</v>
       </c>
       <c r="ER21" s="1" t="n">
-        <v>59.0</v>
+        <v>49.0</v>
       </c>
       <c r="ES21" t="n">
-        <v>10.5</v>
+        <v>1.0</v>
       </c>
       <c r="ET21"/>
       <c r="EU21"/>
       <c r="EV21"/>
       <c r="EW21"/>
       <c r="EX21"/>
-      <c r="EY21" s="3" t="inlineStr">
-        <is>
-          <t>00002143482</t>
-        </is>
-      </c>
-      <c r="EZ21" t="n">
-        <v>9.2</v>
-      </c>
+      <c r="EY21"/>
+      <c r="EZ21"/>
       <c r="FA21" s="4" t="n">
         <v>43548.0</v>
       </c>
       <c r="FB21" s="4" t="n">
-        <v>43548.0</v>
+        <v>43549.0</v>
       </c>
       <c r="FC21" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="FD21"/>
-      <c r="FE21"/>
-      <c r="FF21"/>
+        <v>76.0</v>
+      </c>
+      <c r="FD21" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FE21" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="FF21" s="1" t="n">
+        <v>24.0</v>
+      </c>
       <c r="FG21"/>
-      <c r="FH21"/>
-      <c r="FI21"/>
-      <c r="FJ21"/>
+      <c r="FH21" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FI21" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FJ21" s="1" t="n">
+        <v>25.0</v>
+      </c>
       <c r="FK21"/>
-      <c r="FL21"/>
-      <c r="FM21"/>
-      <c r="FN21"/>
+      <c r="FL21" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="FM21" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="FN21" s="1" t="n">
+        <v>27.0</v>
+      </c>
       <c r="FO21"/>
       <c r="FP21"/>
       <c r="FQ21"/>
@@ -8331,13 +8479,35 @@
       <c r="GF21"/>
       <c r="GG21"/>
       <c r="GH21"/>
-      <c r="GI21"/>
-      <c r="GJ21"/>
-      <c r="GK21"/>
-      <c r="GL21"/>
-      <c r="GM21"/>
-      <c r="GN21"/>
-      <c r="GO21"/>
+      <c r="GI21" s="1" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="GJ21" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="GK21" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_ACTUAL</t>
+        </is>
+      </c>
+      <c r="GL21" s="1" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="GM21" s="3" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="GN21" s="3" t="inlineStr">
+        <is>
+          <t>DEDUCTION</t>
+        </is>
+      </c>
+      <c r="GO21" s="1" t="n">
+        <v>50.0</v>
+      </c>
       <c r="GP21"/>
       <c r="GQ21"/>
       <c r="GR21"/>
@@ -8350,6 +8520,254 @@
       <c r="GY21"/>
       <c r="GZ21"/>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>6a04cbecb80b363c8541f24c</t>
+        </is>
+      </c>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>7722337</t>
+        </is>
+      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>119932404007801</t>
+        </is>
+      </c>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22"/>
+      <c r="AG22"/>
+      <c r="AH22"/>
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22"/>
+      <c r="AL22"/>
+      <c r="AM22"/>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22"/>
+      <c r="AS22"/>
+      <c r="AT22"/>
+      <c r="AU22"/>
+      <c r="AV22"/>
+      <c r="AW22"/>
+      <c r="AX22"/>
+      <c r="AY22"/>
+      <c r="AZ22"/>
+      <c r="BA22"/>
+      <c r="BB22"/>
+      <c r="BC22"/>
+      <c r="BD22"/>
+      <c r="BE22"/>
+      <c r="BF22"/>
+      <c r="BG22"/>
+      <c r="BH22"/>
+      <c r="BI22"/>
+      <c r="BJ22"/>
+      <c r="BK22"/>
+      <c r="BL22"/>
+      <c r="BM22"/>
+      <c r="BN22"/>
+      <c r="BO22"/>
+      <c r="BP22"/>
+      <c r="BQ22"/>
+      <c r="BR22"/>
+      <c r="BS22"/>
+      <c r="BT22"/>
+      <c r="BU22"/>
+      <c r="BV22"/>
+      <c r="BW22"/>
+      <c r="BX22"/>
+      <c r="BY22"/>
+      <c r="BZ22"/>
+      <c r="CA22"/>
+      <c r="CB22"/>
+      <c r="CC22"/>
+      <c r="CD22"/>
+      <c r="CE22"/>
+      <c r="CF22"/>
+      <c r="CG22"/>
+      <c r="CH22"/>
+      <c r="CI22"/>
+      <c r="CJ22"/>
+      <c r="CK22"/>
+      <c r="CL22"/>
+      <c r="CM22"/>
+      <c r="CN22"/>
+      <c r="CO22"/>
+      <c r="CP22"/>
+      <c r="CQ22"/>
+      <c r="CR22"/>
+      <c r="CS22"/>
+      <c r="CT22"/>
+      <c r="CU22"/>
+      <c r="CV22"/>
+      <c r="CW22"/>
+      <c r="CX22"/>
+      <c r="CY22"/>
+      <c r="CZ22"/>
+      <c r="DA22"/>
+      <c r="DB22"/>
+      <c r="DC22"/>
+      <c r="DD22"/>
+      <c r="DE22"/>
+      <c r="DF22"/>
+      <c r="DG22"/>
+      <c r="DH22"/>
+      <c r="DI22"/>
+      <c r="DJ22"/>
+      <c r="DK22"/>
+      <c r="DL22"/>
+      <c r="DM22"/>
+      <c r="DN22"/>
+      <c r="DO22"/>
+      <c r="DP22"/>
+      <c r="DQ22"/>
+      <c r="DR22"/>
+      <c r="DS22"/>
+      <c r="DT22"/>
+      <c r="DU22"/>
+      <c r="DV22"/>
+      <c r="DW22"/>
+      <c r="DX22"/>
+      <c r="DY22"/>
+      <c r="DZ22"/>
+      <c r="EA22"/>
+      <c r="EB22"/>
+      <c r="EC22"/>
+      <c r="ED22"/>
+      <c r="EE22"/>
+      <c r="EF22"/>
+      <c r="EG22"/>
+      <c r="EH22"/>
+      <c r="EI22"/>
+      <c r="EJ22" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="EK22"/>
+      <c r="EL22"/>
+      <c r="EM22"/>
+      <c r="EN22"/>
+      <c r="EO22"/>
+      <c r="EP22" s="3" t="inlineStr">
+        <is>
+          <t>00002143481</t>
+        </is>
+      </c>
+      <c r="EQ22" s="1" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="ER22" s="1" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="ES22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="ET22"/>
+      <c r="EU22"/>
+      <c r="EV22"/>
+      <c r="EW22"/>
+      <c r="EX22"/>
+      <c r="EY22" s="3" t="inlineStr">
+        <is>
+          <t>00002143482</t>
+        </is>
+      </c>
+      <c r="EZ22" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="FA22" s="4" t="n">
+        <v>43548.0</v>
+      </c>
+      <c r="FB22" s="4" t="n">
+        <v>43548.0</v>
+      </c>
+      <c r="FC22" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="FD22"/>
+      <c r="FE22"/>
+      <c r="FF22"/>
+      <c r="FG22"/>
+      <c r="FH22"/>
+      <c r="FI22"/>
+      <c r="FJ22"/>
+      <c r="FK22"/>
+      <c r="FL22"/>
+      <c r="FM22"/>
+      <c r="FN22"/>
+      <c r="FO22"/>
+      <c r="FP22"/>
+      <c r="FQ22"/>
+      <c r="FR22"/>
+      <c r="FS22"/>
+      <c r="FT22"/>
+      <c r="FU22"/>
+      <c r="FV22"/>
+      <c r="FW22"/>
+      <c r="FX22"/>
+      <c r="FY22"/>
+      <c r="FZ22"/>
+      <c r="GA22"/>
+      <c r="GB22"/>
+      <c r="GC22"/>
+      <c r="GD22"/>
+      <c r="GE22"/>
+      <c r="GF22"/>
+      <c r="GG22"/>
+      <c r="GH22"/>
+      <c r="GI22"/>
+      <c r="GJ22"/>
+      <c r="GK22"/>
+      <c r="GL22"/>
+      <c r="GM22"/>
+      <c r="GN22"/>
+      <c r="GO22"/>
+      <c r="GP22"/>
+      <c r="GQ22"/>
+      <c r="GR22"/>
+      <c r="GS22"/>
+      <c r="GT22"/>
+      <c r="GU22"/>
+      <c r="GV22"/>
+      <c r="GW22"/>
+      <c r="GX22"/>
+      <c r="GY22"/>
+      <c r="GZ22"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/converted_files/835/835-all-files.xlsx
+++ b/converted_files/835/835-all-files.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f061</t>
+          <t>6a04cc591ef26d534baf0ce9</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f0c6</t>
+          <t>6a04cc591ef26d534baf0d4e</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f0f8</t>
+          <t>6a04cc591ef26d534baf0d80</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2449,7 +2449,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f0f8</t>
+          <t>6a04cc591ef26d534baf0d80</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2701,7 +2701,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f0f8</t>
+          <t>6a04cc591ef26d534baf0d80</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2953,7 +2953,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f125</t>
+          <t>6a04cc591ef26d534baf0dad</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3413,7 +3413,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f17e</t>
+          <t>6a04cc591ef26d534baf0e06</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f17e</t>
+          <t>6a04cc591ef26d534baf0e06</t>
         </is>
       </c>
       <c r="B9"/>
@@ -4335,7 +4335,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f17e</t>
+          <t>6a04cc591ef26d534baf0e06</t>
         </is>
       </c>
       <c r="B10"/>
@@ -4599,7 +4599,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f17e</t>
+          <t>6a04cc591ef26d534baf0e06</t>
         </is>
       </c>
       <c r="B11"/>
@@ -4863,7 +4863,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f17e</t>
+          <t>6a04cc591ef26d534baf0e06</t>
         </is>
       </c>
       <c r="B12"/>
@@ -5157,7 +5157,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f1b0</t>
+          <t>6a04cc591ef26d534baf0e38</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -5591,7 +5591,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f1b1</t>
+          <t>6a04cc591ef26d534baf0e39</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6025,7 +6025,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f1df</t>
+          <t>6a04cc591ef26d534baf0e67</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6487,7 +6487,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f24c</t>
+          <t>6a04cc591ef26d534baf0ed4</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7189,7 +7189,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f24c</t>
+          <t>6a04cc591ef26d534baf0ed4</t>
         </is>
       </c>
       <c r="B17"/>
@@ -7453,7 +7453,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f24c</t>
+          <t>6a04cc591ef26d534baf0ed4</t>
         </is>
       </c>
       <c r="B18"/>
@@ -7717,7 +7717,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f24c</t>
+          <t>6a04cc591ef26d534baf0ed4</t>
         </is>
       </c>
       <c r="B19"/>
@@ -7981,7 +7981,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f24c</t>
+          <t>6a04cc591ef26d534baf0ed4</t>
         </is>
       </c>
       <c r="B20"/>
@@ -8229,7 +8229,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f24c</t>
+          <t>6a04cc591ef26d534baf0ed4</t>
         </is>
       </c>
       <c r="B21"/>
@@ -8523,7 +8523,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f24c</t>
+          <t>6a04cc591ef26d534baf0ed4</t>
         </is>
       </c>
       <c r="B22"/>

--- a/converted_files/835/835-all-files.xlsx
+++ b/converted_files/835/835-all-files.xlsx
@@ -59,7 +59,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:GZ22"/>
+  <dimension ref="A1:GZ23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ce9</t>
+          <t>6a32cb6297613a0e49906073</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="FE2" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="FF2" s="1" t="n">
@@ -1525,7 +1525,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0d4e</t>
+          <t>6a32cb6297613a0e499060da</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0d80</t>
+          <t>6a32cb6297613a0e4990610e</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2449,7 +2449,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0d80</t>
+          <t>6a32cb6297613a0e4990610e</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2701,7 +2701,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0d80</t>
+          <t>6a32cb6297613a0e4990610e</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2953,7 +2953,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0dad</t>
+          <t>6a32cb6297613a0e4990613d</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3413,7 +3413,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e06</t>
+          <t>6a32cb6297613a0e49906198</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e06</t>
+          <t>6a32cb6297613a0e49906198</t>
         </is>
       </c>
       <c r="B9"/>
@@ -4335,7 +4335,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e06</t>
+          <t>6a32cb6297613a0e49906198</t>
         </is>
       </c>
       <c r="B10"/>
@@ -4599,7 +4599,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e06</t>
+          <t>6a32cb6297613a0e49906198</t>
         </is>
       </c>
       <c r="B11"/>
@@ -4863,7 +4863,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e06</t>
+          <t>6a32cb6297613a0e49906198</t>
         </is>
       </c>
       <c r="B12"/>
@@ -5157,7 +5157,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e38</t>
+          <t>6a32cb6297613a0e499061cc</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -5591,7 +5591,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e39</t>
+          <t>6a32cb6297613a0e499061cd</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6025,7 +6025,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0e67</t>
+          <t>6a32cb6297613a0e499061f8</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6035,39 +6035,41 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>835-denial.dat</t>
+          <t>835-minimal.dat</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>10060875</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>PATACCT</t>
+          <t>5554555444</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>DENIED</t>
+          <t>PRIMARY</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>150.0</v>
+        <v>800.0</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I15"/>
+        <v>500.0</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>300.0</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>CLAIMNUMBER</t>
+          <t>94060555410000</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -6084,7 +6086,7 @@
       <c r="O15"/>
       <c r="P15"/>
       <c r="Q15" s="1" t="n">
-        <v>0.0</v>
+        <v>132.0</v>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
@@ -6093,28 +6095,32 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>NON_PAYMENT</t>
-        </is>
-      </c>
-      <c r="T15"/>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
       <c r="U15" s="4" t="n">
-        <v>43693.0</v>
+        <v>43555.0</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>TRACE123</t>
+          <t>CHECK_1</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>PAYER_ID01</t>
         </is>
       </c>
       <c r="X15" s="4" t="n">
-        <v>43704.0</v>
+        <v>45649.0</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>150.0</v>
+        <v>300.0</v>
       </c>
       <c r="Z15"/>
       <c r="AA15"/>
@@ -6143,7 +6149,7 @@
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>ADDNL_PAYER_ID</t>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
@@ -6210,8 +6216,16 @@
           <t>EDI.SUPPORT@ANYPAYER.COM</t>
         </is>
       </c>
-      <c r="BL15"/>
-      <c r="BM15"/>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BM15" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
       <c r="BN15"/>
       <c r="BO15"/>
       <c r="BP15" s="3" t="inlineStr">
@@ -6221,7 +6235,7 @@
       </c>
       <c r="BQ15" s="3" t="inlineStr">
         <is>
-          <t>1123454567</t>
+          <t>PROVIDER2_NPI</t>
         </is>
       </c>
       <c r="BR15" s="3" t="inlineStr">
@@ -6251,8 +6265,16 @@
         </is>
       </c>
       <c r="BX15"/>
-      <c r="BY15"/>
-      <c r="BZ15"/>
+      <c r="BY15" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BZ15" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID2</t>
+        </is>
+      </c>
       <c r="CA15"/>
       <c r="CB15"/>
       <c r="CC15" s="3" t="inlineStr">
@@ -6262,24 +6284,20 @@
       </c>
       <c r="CD15" s="3" t="inlineStr">
         <is>
-          <t>ABC123456789</t>
+          <t>33344555510</t>
         </is>
       </c>
       <c r="CE15" s="3" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>BUDD</t>
         </is>
       </c>
       <c r="CF15" s="3" t="inlineStr">
         <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CG15" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>WILLIAM</t>
+        </is>
+      </c>
+      <c r="CG15"/>
       <c r="CH15" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -6287,24 +6305,20 @@
       </c>
       <c r="CI15" s="3" t="inlineStr">
         <is>
-          <t>ABC123456789</t>
+          <t>33344555510</t>
         </is>
       </c>
       <c r="CJ15" s="3" t="inlineStr">
         <is>
-          <t>DOE</t>
+          <t>BUDD</t>
         </is>
       </c>
       <c r="CK15" s="3" t="inlineStr">
         <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="CL15" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>WILLIAM</t>
+        </is>
+      </c>
+      <c r="CL15"/>
       <c r="CM15"/>
       <c r="CN15"/>
       <c r="CO15"/>
@@ -6336,33 +6350,19 @@
       <c r="DO15"/>
       <c r="DP15"/>
       <c r="DQ15" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="DR15" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="DS15"/>
       <c r="DT15"/>
       <c r="DU15"/>
-      <c r="DV15" s="4" t="n">
-        <v>43505.0</v>
-      </c>
-      <c r="DW15" s="1" t="n">
-        <v>150.0</v>
-      </c>
-      <c r="DX15" s="3" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="DY15" s="3" t="inlineStr">
-        <is>
-          <t>COVERAGE_AMOUNT</t>
-        </is>
-      </c>
-      <c r="DZ15" s="1" t="n">
-        <v>150.0</v>
-      </c>
+      <c r="DV15"/>
+      <c r="DW15"/>
+      <c r="DX15"/>
+      <c r="DY15"/>
+      <c r="DZ15"/>
       <c r="EA15"/>
       <c r="EB15"/>
       <c r="EC15"/>
@@ -6374,12 +6374,12 @@
       <c r="EI15"/>
       <c r="EJ15" s="3" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1</t>
         </is>
       </c>
       <c r="EK15" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>99211</t>
         </is>
       </c>
       <c r="EL15"/>
@@ -6388,10 +6388,10 @@
       <c r="EO15"/>
       <c r="EP15"/>
       <c r="EQ15" s="1" t="n">
-        <v>150.0</v>
+        <v>800.0</v>
       </c>
       <c r="ER15" s="1" t="n">
-        <v>0.0</v>
+        <v>500.0</v>
       </c>
       <c r="ES15" t="n">
         <v>1.0</v>
@@ -6404,26 +6404,26 @@
       <c r="EY15"/>
       <c r="EZ15"/>
       <c r="FA15" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="FB15" s="4" t="n">
-        <v>43466.0</v>
+        <v>45352.0</v>
       </c>
       <c r="FC15" s="1" t="n">
-        <v>150.0</v>
+        <v>300.0</v>
       </c>
       <c r="FD15" s="3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PATIENT_RESPONSIBILITY</t>
         </is>
       </c>
       <c r="FE15" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FF15" s="1" t="n">
-        <v>150.0</v>
+        <v>300.0</v>
       </c>
       <c r="FG15"/>
       <c r="FH15"/>
@@ -6449,22 +6449,26 @@
       <c r="GB15"/>
       <c r="GC15"/>
       <c r="GD15"/>
-      <c r="GE15" s="3" t="inlineStr">
-        <is>
-          <t>CMS_NPI</t>
-        </is>
-      </c>
-      <c r="GF15" s="3" t="inlineStr">
-        <is>
-          <t>99123</t>
-        </is>
-      </c>
+      <c r="GE15"/>
+      <c r="GF15"/>
       <c r="GG15"/>
       <c r="GH15"/>
-      <c r="GI15"/>
-      <c r="GJ15"/>
-      <c r="GK15"/>
-      <c r="GL15"/>
+      <c r="GI15" s="1" t="n">
+        <v>800.0</v>
+      </c>
+      <c r="GJ15" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="GK15" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_ACTUAL</t>
+        </is>
+      </c>
+      <c r="GL15" s="1" t="n">
+        <v>800.0</v>
+      </c>
       <c r="GM15"/>
       <c r="GN15"/>
       <c r="GO15"/>
@@ -6474,11 +6478,7 @@
       <c r="GS15"/>
       <c r="GT15"/>
       <c r="GU15"/>
-      <c r="GV15" s="3" t="inlineStr">
-        <is>
-          <t>M143</t>
-        </is>
-      </c>
+      <c r="GV15"/>
       <c r="GW15"/>
       <c r="GX15"/>
       <c r="GY15"/>
@@ -6487,7 +6487,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ed4</t>
+          <t>6a32cb6297613a0e49906228</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -6497,41 +6497,39 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>835-all-fields.dat</t>
+          <t>835-denial.dat</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>10060875</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>7722337</t>
+          <t>PATACCT</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>DENIED</t>
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>226.0</v>
+        <v>150.0</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>132.0</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>10.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="I16"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>119932404007801</t>
+          <t>CLAIMNUMBER</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -6544,19 +6542,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
       <c r="Q16" s="1" t="n">
-        <v>132.0</v>
+        <v>0.0</v>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
@@ -6565,76 +6555,40 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>ACH</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>2200008888</t>
-        </is>
-      </c>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="T16"/>
       <c r="U16" s="4" t="n">
-        <v>45756.0</v>
+        <v>43693.0</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>882509401093167</t>
+          <t>TRACE123</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>106609999</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="X16" s="4" t="n">
-        <v>43538.0</v>
+        <v>43704.0</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>32405.0</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="AA16" s="3" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="AB16" s="1" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="AE16" s="3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AF16" s="1" t="n">
-        <v>30000.0</v>
-      </c>
+        <v>150.0</v>
+      </c>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
       <c r="AG16"/>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="AI16" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AJ16" s="1" t="n">
-        <v>259.0</v>
-      </c>
+      <c r="AH16"/>
+      <c r="AI16"/>
+      <c r="AJ16"/>
       <c r="AK16"/>
       <c r="AL16"/>
       <c r="AM16"/>
@@ -6651,40 +6605,36 @@
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>DELTA DENTAL OF ABC</t>
+          <t>ANY PLAN USA</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>225 MAIN STREET</t>
+          <t>1 WALK THIS WAY</t>
         </is>
       </c>
       <c r="AX16"/>
       <c r="AY16" s="3" t="inlineStr">
         <is>
-          <t>CENTERVILLE</t>
+          <t>ANYCITY</t>
         </is>
       </c>
       <c r="AZ16" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="BA16" s="3" t="inlineStr">
         <is>
-          <t>17111</t>
-        </is>
-      </c>
-      <c r="BB16" s="3" t="inlineStr">
-        <is>
-          <t>JANE DOE</t>
-        </is>
-      </c>
+          <t>45209</t>
+        </is>
+      </c>
+      <c r="BB16"/>
       <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>PHONE</t>
@@ -6692,103 +6642,91 @@
       </c>
       <c r="BD16" s="3" t="inlineStr">
         <is>
-          <t>9005555555</t>
-        </is>
-      </c>
-      <c r="BE16" s="3" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="BF16" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="BG16"/>
+          <t>8661112222</t>
+        </is>
+      </c>
+      <c r="BE16"/>
+      <c r="BF16"/>
+      <c r="BG16" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
       <c r="BH16" s="3" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>PHONE</t>
         </is>
       </c>
       <c r="BI16" s="3" t="inlineStr">
         <is>
-          <t>myplan.com/policies</t>
-        </is>
-      </c>
-      <c r="BJ16"/>
-      <c r="BK16"/>
-      <c r="BL16" s="3" t="inlineStr">
-        <is>
-          <t>PAYER_IDENTIFICATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="BM16" s="3" t="inlineStr">
-        <is>
-          <t>0101</t>
-        </is>
-      </c>
-      <c r="BN16" s="3" t="inlineStr">
-        <is>
-          <t>HEALTH_INDUSTRY_NUMBER</t>
-        </is>
-      </c>
-      <c r="BO16" s="3" t="inlineStr">
-        <is>
-          <t>0202</t>
-        </is>
-      </c>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="BJ16" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="BL16"/>
+      <c r="BM16"/>
+      <c r="BN16"/>
+      <c r="BO16"/>
       <c r="BP16" s="3" t="inlineStr">
         <is>
-          <t>EIN</t>
+          <t>NPI</t>
         </is>
       </c>
       <c r="BQ16" s="3" t="inlineStr">
         <is>
-          <t>999994703</t>
+          <t>1123454567</t>
         </is>
       </c>
       <c r="BR16" s="3" t="inlineStr">
         <is>
-          <t>BAN DDS LLC</t>
+          <t>PROVIDER</t>
         </is>
       </c>
       <c r="BS16" s="3" t="inlineStr">
         <is>
-          <t>225 MAIN STREET</t>
+          <t>2255 ANY ROAD</t>
         </is>
       </c>
       <c r="BT16"/>
       <c r="BU16" s="3" t="inlineStr">
         <is>
-          <t>CENTERVILLE</t>
+          <t>ANY CITY</t>
         </is>
       </c>
       <c r="BV16" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="BW16" s="3" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="BX16"/>
-      <c r="BY16" s="3" t="inlineStr">
-        <is>
-          <t>PAYEE_IDENTIFICATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="BZ16" s="3" t="inlineStr">
-        <is>
-          <t>0505</t>
-        </is>
-      </c>
+      <c r="BY16"/>
+      <c r="BZ16"/>
       <c r="CA16"/>
       <c r="CB16"/>
-      <c r="CC16"/>
-      <c r="CD16"/>
+      <c r="CC16" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CD16" s="3" t="inlineStr">
+        <is>
+          <t>ABC123456789</t>
+        </is>
+      </c>
       <c r="CE16" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
@@ -6796,10 +6734,14 @@
       </c>
       <c r="CF16" s="3" t="inlineStr">
         <is>
-          <t>SALLY</t>
-        </is>
-      </c>
-      <c r="CG16"/>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CG16" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="CH16" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -6807,7 +6749,7 @@
       </c>
       <c r="CI16" s="3" t="inlineStr">
         <is>
-          <t>SJD11111</t>
+          <t>ABC123456789</t>
         </is>
       </c>
       <c r="CJ16" s="3" t="inlineStr">
@@ -6817,136 +6759,58 @@
       </c>
       <c r="CK16" s="3" t="inlineStr">
         <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="CL16"/>
-      <c r="CM16" s="3" t="inlineStr">
-        <is>
-          <t>INSURED_CHANGED_ID</t>
-        </is>
-      </c>
-      <c r="CN16" s="3" t="inlineStr">
-        <is>
-          <t>SJD999</t>
-        </is>
-      </c>
-      <c r="CO16" s="3" t="inlineStr">
-        <is>
-          <t>Due</t>
-        </is>
-      </c>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="CL16" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="CM16"/>
+      <c r="CN16"/>
+      <c r="CO16"/>
       <c r="CP16"/>
       <c r="CQ16"/>
-      <c r="CR16" s="3" t="inlineStr">
-        <is>
-          <t>NPI</t>
-        </is>
-      </c>
-      <c r="CS16" s="3" t="inlineStr">
-        <is>
-          <t>1811901945</t>
-        </is>
-      </c>
-      <c r="CT16" s="3" t="inlineStr">
-        <is>
-          <t>BAN</t>
-        </is>
-      </c>
-      <c r="CU16" s="3" t="inlineStr">
-        <is>
-          <t>ERIN</t>
-        </is>
-      </c>
+      <c r="CR16"/>
+      <c r="CS16"/>
+      <c r="CT16"/>
+      <c r="CU16"/>
       <c r="CV16"/>
       <c r="CW16"/>
-      <c r="CX16" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_PROVIDER_NUMBER</t>
-        </is>
-      </c>
-      <c r="CY16" s="3" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="CZ16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="DA16" s="3" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="DB16" s="3" t="inlineStr">
-        <is>
-          <t>CMS_PLAN_ID</t>
-        </is>
-      </c>
-      <c r="DC16" s="3" t="inlineStr">
-        <is>
-          <t>9876</t>
-        </is>
-      </c>
-      <c r="DD16" s="3" t="inlineStr">
-        <is>
-          <t>ACME INSURANCE</t>
-        </is>
-      </c>
-      <c r="DE16" s="3" t="inlineStr">
-        <is>
-          <t>CMS_PLAN_ID</t>
-        </is>
-      </c>
-      <c r="DF16" s="3" t="inlineStr">
-        <is>
-          <t>8765</t>
-        </is>
-      </c>
-      <c r="DG16" s="3" t="inlineStr">
-        <is>
-          <t>ACME INSURANCE</t>
-        </is>
-      </c>
+      <c r="CX16"/>
+      <c r="CY16"/>
+      <c r="CZ16"/>
+      <c r="DA16"/>
+      <c r="DB16"/>
+      <c r="DC16"/>
+      <c r="DD16"/>
+      <c r="DE16"/>
+      <c r="DF16"/>
+      <c r="DG16"/>
       <c r="DH16"/>
       <c r="DI16"/>
-      <c r="DJ16" s="3" t="inlineStr">
-        <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="DK16" s="3" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
+      <c r="DJ16"/>
+      <c r="DK16"/>
       <c r="DL16"/>
       <c r="DM16"/>
       <c r="DN16"/>
       <c r="DO16"/>
       <c r="DP16"/>
       <c r="DQ16" s="4" t="n">
-        <v>43548.0</v>
+        <v>43466.0</v>
       </c>
       <c r="DR16" s="4" t="n">
-        <v>43549.0</v>
-      </c>
-      <c r="DS16" s="4" t="n">
-        <v>44819.0</v>
-      </c>
-      <c r="DT16" s="4" t="n">
-        <v>44820.0</v>
-      </c>
-      <c r="DU16" s="4" t="n">
-        <v>44835.0</v>
-      </c>
+        <v>43466.0</v>
+      </c>
+      <c r="DS16"/>
+      <c r="DT16"/>
+      <c r="DU16"/>
       <c r="DV16" s="4" t="n">
-        <v>44889.0</v>
+        <v>43505.0</v>
       </c>
       <c r="DW16" s="1" t="n">
-        <v>132.0</v>
+        <v>150.0</v>
       </c>
       <c r="DX16" s="3" t="inlineStr">
         <is>
@@ -6959,111 +6823,69 @@
         </is>
       </c>
       <c r="DZ16" s="1" t="n">
-        <v>132.0</v>
-      </c>
-      <c r="EA16" s="3" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="EB16" s="3" t="inlineStr">
-        <is>
-          <t>DISCOUNT_AMOUNT</t>
-        </is>
-      </c>
-      <c r="EC16" s="1" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="ED16" s="3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="EE16" s="3" t="inlineStr">
-        <is>
-          <t>COVERED</t>
-        </is>
-      </c>
-      <c r="EF16" t="n">
-        <v>4.0</v>
-      </c>
+        <v>150.0</v>
+      </c>
+      <c r="EA16"/>
+      <c r="EB16"/>
+      <c r="EC16"/>
+      <c r="ED16"/>
+      <c r="EE16"/>
+      <c r="EF16"/>
       <c r="EG16"/>
       <c r="EH16"/>
       <c r="EI16"/>
       <c r="EJ16" s="3" t="inlineStr">
         <is>
-          <t>A123</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="EK16" s="3" t="inlineStr">
         <is>
-          <t>D0120</t>
-        </is>
-      </c>
-      <c r="EL16" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="EM16" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>99213</t>
+        </is>
+      </c>
+      <c r="EL16"/>
+      <c r="EM16"/>
       <c r="EN16"/>
-      <c r="EO16" s="3" t="inlineStr">
-        <is>
-          <t>0022</t>
-        </is>
-      </c>
+      <c r="EO16"/>
       <c r="EP16"/>
       <c r="EQ16" s="1" t="n">
-        <v>46.0</v>
+        <v>150.0</v>
       </c>
       <c r="ER16" s="1" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="ES16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="ET16" s="3" t="inlineStr">
-        <is>
-          <t>D0140</t>
-        </is>
-      </c>
-      <c r="EU16" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="ET16"/>
+      <c r="EU16"/>
       <c r="EV16"/>
       <c r="EW16"/>
       <c r="EX16"/>
       <c r="EY16"/>
-      <c r="EZ16" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="EZ16"/>
       <c r="FA16" s="4" t="n">
-        <v>43548.0</v>
+        <v>43466.0</v>
       </c>
       <c r="FB16" s="4" t="n">
-        <v>43548.0</v>
+        <v>43466.0</v>
       </c>
       <c r="FC16" s="1" t="n">
-        <v>21.0</v>
+        <v>150.0</v>
       </c>
       <c r="FD16" s="3" t="inlineStr">
         <is>
-          <t>CONTRACTUAL</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="FE16" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>252</t>
         </is>
       </c>
       <c r="FF16" s="1" t="n">
-        <v>21.0</v>
+        <v>150.0</v>
       </c>
       <c r="FG16"/>
       <c r="FH16"/>
@@ -7082,41 +6904,13 @@
       <c r="FU16"/>
       <c r="FV16"/>
       <c r="FW16"/>
-      <c r="FX16" s="3" t="inlineStr">
-        <is>
-          <t>RATE_CODE_NUMBER</t>
-        </is>
-      </c>
-      <c r="FY16" s="3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="FZ16" s="3" t="inlineStr">
-        <is>
-          <t>APG_NUMBER</t>
-        </is>
-      </c>
-      <c r="GA16" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="GB16" s="3" t="inlineStr">
-        <is>
-          <t>AMBULATORY_PAYMENT</t>
-        </is>
-      </c>
-      <c r="GC16" s="3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="GD16" s="3" t="inlineStr">
-        <is>
-          <t>1234"5</t>
-        </is>
-      </c>
+      <c r="FX16"/>
+      <c r="FY16"/>
+      <c r="FZ16"/>
+      <c r="GA16"/>
+      <c r="GB16"/>
+      <c r="GC16"/>
+      <c r="GD16"/>
       <c r="GE16" s="3" t="inlineStr">
         <is>
           <t>CMS_NPI</t>
@@ -7124,64 +6918,30 @@
       </c>
       <c r="GF16" s="3" t="inlineStr">
         <is>
-          <t>P123</t>
-        </is>
-      </c>
-      <c r="GG16" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_PROVIDER_NUMBER</t>
-        </is>
-      </c>
-      <c r="GH16" s="3" t="inlineStr">
-        <is>
-          <t>P234</t>
-        </is>
-      </c>
-      <c r="GI16" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="GJ16" s="3" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="GK16" s="3" t="inlineStr">
-        <is>
-          <t>ALLOWED_ACTUAL</t>
-        </is>
-      </c>
-      <c r="GL16" s="1" t="n">
-        <v>25.0</v>
-      </c>
+          <t>99123</t>
+        </is>
+      </c>
+      <c r="GG16"/>
+      <c r="GH16"/>
+      <c r="GI16"/>
+      <c r="GJ16"/>
+      <c r="GK16"/>
+      <c r="GL16"/>
       <c r="GM16"/>
       <c r="GN16"/>
       <c r="GO16"/>
-      <c r="GP16" s="3" t="inlineStr">
-        <is>
-          <t>ZL</t>
-        </is>
-      </c>
-      <c r="GQ16" s="3" t="inlineStr">
-        <is>
-          <t>MEDICARE_MEDICAID_CAT_2</t>
-        </is>
-      </c>
-      <c r="GR16" t="n">
-        <v>3.75</v>
-      </c>
+      <c r="GP16"/>
+      <c r="GQ16"/>
+      <c r="GR16"/>
       <c r="GS16"/>
       <c r="GT16"/>
       <c r="GU16"/>
       <c r="GV16" s="3" t="inlineStr">
         <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="GW16" s="3" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
+          <t>M143</t>
+        </is>
+      </c>
+      <c r="GW16"/>
       <c r="GX16"/>
       <c r="GY16"/>
       <c r="GZ16"/>
@@ -7189,52 +6949,154 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ed4</t>
-        </is>
-      </c>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
+          <t>6a32cb6297613a0e4990628b</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>835-all-fields.dat</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>35681</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>7722337</t>
         </is>
       </c>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>384.0</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>238.0</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>119932404007801</t>
         </is>
       </c>
-      <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="R17"/>
-      <c r="S17"/>
-      <c r="T17"/>
-      <c r="U17"/>
-      <c r="V17"/>
-      <c r="W17"/>
-      <c r="X17"/>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17"/>
-      <c r="AB17"/>
-      <c r="AC17"/>
-      <c r="AD17"/>
-      <c r="AE17"/>
-      <c r="AF17"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>43555.0</v>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>1512345678</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>43538.0</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>32405.0</v>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>30000.0</v>
+      </c>
       <c r="AG17"/>
-      <c r="AH17"/>
-      <c r="AI17"/>
-      <c r="AJ17"/>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AJ17" s="1" t="n">
+        <v>259.0</v>
+      </c>
       <c r="AK17"/>
       <c r="AL17"/>
       <c r="AM17"/>
@@ -7244,131 +7106,397 @@
       <c r="AQ17"/>
       <c r="AR17"/>
       <c r="AS17"/>
-      <c r="AT17"/>
-      <c r="AU17"/>
-      <c r="AV17"/>
-      <c r="AW17"/>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>DELTA DENTAL OF ABC</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
       <c r="AX17"/>
-      <c r="AY17"/>
-      <c r="AZ17"/>
-      <c r="BA17"/>
-      <c r="BB17"/>
-      <c r="BC17"/>
-      <c r="BD17"/>
-      <c r="BE17"/>
-      <c r="BF17"/>
+      <c r="AY17" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="AZ17" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="BA17" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
+      <c r="BB17" s="3" t="inlineStr">
+        <is>
+          <t>JANE DOE</t>
+        </is>
+      </c>
+      <c r="BC17" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="BD17" s="3" t="inlineStr">
+        <is>
+          <t>9005555555</t>
+        </is>
+      </c>
+      <c r="BE17" s="3" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="BF17" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
       <c r="BG17"/>
-      <c r="BH17"/>
-      <c r="BI17"/>
+      <c r="BH17" s="3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="BI17" s="3" t="inlineStr">
+        <is>
+          <t>myplan.com/policies</t>
+        </is>
+      </c>
       <c r="BJ17"/>
       <c r="BK17"/>
-      <c r="BL17"/>
-      <c r="BM17"/>
-      <c r="BN17"/>
-      <c r="BO17"/>
-      <c r="BP17"/>
-      <c r="BQ17"/>
-      <c r="BR17"/>
-      <c r="BS17"/>
+      <c r="BL17" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BM17" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="BN17" s="3" t="inlineStr">
+        <is>
+          <t>HEALTH_INDUSTRY_NUMBER</t>
+        </is>
+      </c>
+      <c r="BO17" s="3" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="BP17" s="3" t="inlineStr">
+        <is>
+          <t>EIN</t>
+        </is>
+      </c>
+      <c r="BQ17" s="3" t="inlineStr">
+        <is>
+          <t>999994703</t>
+        </is>
+      </c>
+      <c r="BR17" s="3" t="inlineStr">
+        <is>
+          <t>BAN DDS LLC</t>
+        </is>
+      </c>
+      <c r="BS17" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
       <c r="BT17"/>
-      <c r="BU17"/>
-      <c r="BV17"/>
-      <c r="BW17"/>
+      <c r="BU17" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="BV17" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="BW17" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
       <c r="BX17"/>
-      <c r="BY17"/>
-      <c r="BZ17"/>
+      <c r="BY17" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="BZ17" s="3" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
       <c r="CA17"/>
       <c r="CB17"/>
       <c r="CC17"/>
       <c r="CD17"/>
-      <c r="CE17"/>
-      <c r="CF17"/>
+      <c r="CE17" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CF17" s="3" t="inlineStr">
+        <is>
+          <t>SALLY</t>
+        </is>
+      </c>
       <c r="CG17"/>
-      <c r="CH17"/>
-      <c r="CI17"/>
-      <c r="CJ17"/>
-      <c r="CK17"/>
+      <c r="CH17" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="CI17" s="3" t="inlineStr">
+        <is>
+          <t>SJD11111</t>
+        </is>
+      </c>
+      <c r="CJ17" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CK17" s="3" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
       <c r="CL17"/>
-      <c r="CM17"/>
-      <c r="CN17"/>
-      <c r="CO17"/>
+      <c r="CM17" s="3" t="inlineStr">
+        <is>
+          <t>INSURED_CHANGED_ID</t>
+        </is>
+      </c>
+      <c r="CN17" s="3" t="inlineStr">
+        <is>
+          <t>SJD999</t>
+        </is>
+      </c>
+      <c r="CO17" s="3" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
       <c r="CP17"/>
       <c r="CQ17"/>
-      <c r="CR17"/>
-      <c r="CS17"/>
-      <c r="CT17"/>
-      <c r="CU17"/>
+      <c r="CR17" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="CS17" s="3" t="inlineStr">
+        <is>
+          <t>1811901945</t>
+        </is>
+      </c>
+      <c r="CT17" s="3" t="inlineStr">
+        <is>
+          <t>BAN</t>
+        </is>
+      </c>
+      <c r="CU17" s="3" t="inlineStr">
+        <is>
+          <t>ERIN</t>
+        </is>
+      </c>
       <c r="CV17"/>
       <c r="CW17"/>
-      <c r="CX17"/>
-      <c r="CY17"/>
+      <c r="CX17" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_PROVIDER_NUMBER</t>
+        </is>
+      </c>
+      <c r="CY17" s="3" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
       <c r="CZ17"/>
       <c r="DA17"/>
-      <c r="DB17"/>
-      <c r="DC17"/>
-      <c r="DD17"/>
-      <c r="DE17"/>
-      <c r="DF17"/>
-      <c r="DG17"/>
+      <c r="DB17" s="3" t="inlineStr">
+        <is>
+          <t>CMS_PLAN_ID</t>
+        </is>
+      </c>
+      <c r="DC17" s="3" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="DD17" s="3" t="inlineStr">
+        <is>
+          <t>ACME INSURANCE</t>
+        </is>
+      </c>
+      <c r="DE17" s="3" t="inlineStr">
+        <is>
+          <t>CMS_PLAN_ID</t>
+        </is>
+      </c>
+      <c r="DF17" s="3" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="DG17" s="3" t="inlineStr">
+        <is>
+          <t>ACME INSURANCE</t>
+        </is>
+      </c>
       <c r="DH17"/>
       <c r="DI17"/>
-      <c r="DJ17"/>
-      <c r="DK17"/>
+      <c r="DJ17" s="3" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="DK17" s="3" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
       <c r="DL17"/>
       <c r="DM17"/>
       <c r="DN17"/>
       <c r="DO17"/>
       <c r="DP17"/>
-      <c r="DQ17"/>
-      <c r="DR17"/>
-      <c r="DS17"/>
-      <c r="DT17"/>
-      <c r="DU17"/>
-      <c r="DV17"/>
-      <c r="DW17"/>
-      <c r="DX17"/>
-      <c r="DY17"/>
-      <c r="DZ17"/>
-      <c r="EA17"/>
-      <c r="EB17"/>
-      <c r="EC17"/>
-      <c r="ED17"/>
-      <c r="EE17"/>
-      <c r="EF17"/>
+      <c r="DQ17" s="4" t="n">
+        <v>43548.0</v>
+      </c>
+      <c r="DR17" s="4" t="n">
+        <v>43549.0</v>
+      </c>
+      <c r="DS17" s="4" t="n">
+        <v>44819.0</v>
+      </c>
+      <c r="DT17" s="4" t="n">
+        <v>44820.0</v>
+      </c>
+      <c r="DU17" s="4" t="n">
+        <v>44835.0</v>
+      </c>
+      <c r="DV17" s="4" t="n">
+        <v>44889.0</v>
+      </c>
+      <c r="DW17" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="DX17" s="3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="DY17" s="3" t="inlineStr">
+        <is>
+          <t>COVERAGE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="DZ17" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="EA17" s="3" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="EB17" s="3" t="inlineStr">
+        <is>
+          <t>DISCOUNT_AMOUNT</t>
+        </is>
+      </c>
+      <c r="EC17" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="ED17" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="EE17" s="3" t="inlineStr">
+        <is>
+          <t>COVERED</t>
+        </is>
+      </c>
+      <c r="EF17" t="n">
+        <v>4.0</v>
+      </c>
       <c r="EG17"/>
       <c r="EH17"/>
       <c r="EI17"/>
       <c r="EJ17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>A123</t>
         </is>
       </c>
       <c r="EK17" s="3" t="inlineStr">
         <is>
-          <t>D0220</t>
-        </is>
-      </c>
-      <c r="EL17"/>
-      <c r="EM17"/>
+          <t>D0120</t>
+        </is>
+      </c>
+      <c r="EL17" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="EM17" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="EN17"/>
-      <c r="EO17"/>
+      <c r="EO17" s="3" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
       <c r="EP17"/>
       <c r="EQ17" s="1" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="ER17" s="1" t="n">
         <v>25.0</v>
       </c>
-      <c r="ER17" s="1" t="n">
-        <v>14.0</v>
-      </c>
       <c r="ES17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="ET17"/>
-      <c r="EU17"/>
+        <v>3.1</v>
+      </c>
+      <c r="ET17" s="3" t="inlineStr">
+        <is>
+          <t>D0140</t>
+        </is>
+      </c>
+      <c r="EU17" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="EV17"/>
       <c r="EW17"/>
       <c r="EX17"/>
       <c r="EY17"/>
-      <c r="EZ17"/>
+      <c r="EZ17" t="n">
+        <v>3.5</v>
+      </c>
       <c r="FA17" s="4" t="n">
         <v>43548.0</v>
       </c>
@@ -7376,7 +7504,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC17" s="1" t="n">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="FD17" s="3" t="inlineStr">
         <is>
@@ -7389,7 +7517,7 @@
         </is>
       </c>
       <c r="FF17" s="1" t="n">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="FG17"/>
       <c r="FH17"/>
@@ -7408,19 +7536,63 @@
       <c r="FU17"/>
       <c r="FV17"/>
       <c r="FW17"/>
-      <c r="FX17"/>
-      <c r="FY17"/>
-      <c r="FZ17"/>
-      <c r="GA17"/>
-      <c r="GB17"/>
-      <c r="GC17"/>
-      <c r="GD17"/>
-      <c r="GE17"/>
-      <c r="GF17"/>
-      <c r="GG17"/>
-      <c r="GH17"/>
+      <c r="FX17" s="3" t="inlineStr">
+        <is>
+          <t>RATE_CODE_NUMBER</t>
+        </is>
+      </c>
+      <c r="FY17" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="FZ17" s="3" t="inlineStr">
+        <is>
+          <t>APG_NUMBER</t>
+        </is>
+      </c>
+      <c r="GA17" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="GB17" s="3" t="inlineStr">
+        <is>
+          <t>AMBULATORY_PAYMENT</t>
+        </is>
+      </c>
+      <c r="GC17" s="3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="GD17" s="3" t="inlineStr">
+        <is>
+          <t>1234"5</t>
+        </is>
+      </c>
+      <c r="GE17" s="3" t="inlineStr">
+        <is>
+          <t>CMS_NPI</t>
+        </is>
+      </c>
+      <c r="GF17" s="3" t="inlineStr">
+        <is>
+          <t>P123</t>
+        </is>
+      </c>
+      <c r="GG17" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_PROVIDER_NUMBER</t>
+        </is>
+      </c>
+      <c r="GH17" s="3" t="inlineStr">
+        <is>
+          <t>P234</t>
+        </is>
+      </c>
       <c r="GI17" s="1" t="n">
-        <v>14.0</v>
+        <v>25.0</v>
       </c>
       <c r="GJ17" s="3" t="inlineStr">
         <is>
@@ -7433,19 +7605,37 @@
         </is>
       </c>
       <c r="GL17" s="1" t="n">
-        <v>14.0</v>
+        <v>25.0</v>
       </c>
       <c r="GM17"/>
       <c r="GN17"/>
       <c r="GO17"/>
-      <c r="GP17"/>
-      <c r="GQ17"/>
-      <c r="GR17"/>
+      <c r="GP17" s="3" t="inlineStr">
+        <is>
+          <t>ZL</t>
+        </is>
+      </c>
+      <c r="GQ17" s="3" t="inlineStr">
+        <is>
+          <t>MEDICARE_MEDICAID_CAT_2</t>
+        </is>
+      </c>
+      <c r="GR17" t="n">
+        <v>3.75</v>
+      </c>
       <c r="GS17"/>
       <c r="GT17"/>
       <c r="GU17"/>
-      <c r="GV17"/>
-      <c r="GW17"/>
+      <c r="GV17" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="GW17" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
       <c r="GX17"/>
       <c r="GY17"/>
       <c r="GZ17"/>
@@ -7453,7 +7643,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ed4</t>
+          <t>6a32cb6297613a0e4990628b</t>
         </is>
       </c>
       <c r="B18"/>
@@ -7604,12 +7794,12 @@
       <c r="EI18"/>
       <c r="EJ18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="EK18" s="3" t="inlineStr">
         <is>
-          <t>D0230</t>
+          <t>D0220</t>
         </is>
       </c>
       <c r="EL18"/>
@@ -7618,10 +7808,10 @@
       <c r="EO18"/>
       <c r="EP18"/>
       <c r="EQ18" s="1" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="ER18" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="ES18" t="n">
         <v>1.0</v>
@@ -7640,7 +7830,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC18" s="1" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="FD18" s="3" t="inlineStr">
         <is>
@@ -7653,7 +7843,7 @@
         </is>
       </c>
       <c r="FF18" s="1" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="FG18"/>
       <c r="FH18"/>
@@ -7684,7 +7874,7 @@
       <c r="GG18"/>
       <c r="GH18"/>
       <c r="GI18" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="GJ18" s="3" t="inlineStr">
         <is>
@@ -7697,7 +7887,7 @@
         </is>
       </c>
       <c r="GL18" s="1" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="GM18"/>
       <c r="GN18"/>
@@ -7717,7 +7907,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ed4</t>
+          <t>6a32cb6297613a0e4990628b</t>
         </is>
       </c>
       <c r="B19"/>
@@ -7868,12 +8058,12 @@
       <c r="EI19"/>
       <c r="EJ19" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EK19" s="3" t="inlineStr">
         <is>
-          <t>D0274</t>
+          <t>D0230</t>
         </is>
       </c>
       <c r="EL19"/>
@@ -7882,10 +8072,10 @@
       <c r="EO19"/>
       <c r="EP19"/>
       <c r="EQ19" s="1" t="n">
-        <v>60.0</v>
+        <v>22.0</v>
       </c>
       <c r="ER19" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="ES19" t="n">
         <v>1.0</v>
@@ -7904,7 +8094,7 @@
         <v>43548.0</v>
       </c>
       <c r="FC19" s="1" t="n">
-        <v>26.0</v>
+        <v>12.0</v>
       </c>
       <c r="FD19" s="3" t="inlineStr">
         <is>
@@ -7917,7 +8107,7 @@
         </is>
       </c>
       <c r="FF19" s="1" t="n">
-        <v>26.0</v>
+        <v>12.0</v>
       </c>
       <c r="FG19"/>
       <c r="FH19"/>
@@ -7948,7 +8138,7 @@
       <c r="GG19"/>
       <c r="GH19"/>
       <c r="GI19" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="GJ19" s="3" t="inlineStr">
         <is>
@@ -7961,7 +8151,7 @@
         </is>
       </c>
       <c r="GL19" s="1" t="n">
-        <v>34.0</v>
+        <v>10.0</v>
       </c>
       <c r="GM19"/>
       <c r="GN19"/>
@@ -7981,7 +8171,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ed4</t>
+          <t>6a32cb6297613a0e4990628b</t>
         </is>
       </c>
       <c r="B20"/>
@@ -8132,24 +8322,24 @@
       <c r="EI20"/>
       <c r="EJ20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="EK20"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="EK20" s="3" t="inlineStr">
+        <is>
+          <t>D0274</t>
+        </is>
+      </c>
       <c r="EL20"/>
       <c r="EM20"/>
       <c r="EN20"/>
-      <c r="EO20" s="3" t="inlineStr">
-        <is>
-          <t>0022</t>
-        </is>
-      </c>
+      <c r="EO20"/>
       <c r="EP20"/>
       <c r="EQ20" s="1" t="n">
-        <v>99.0</v>
+        <v>60.0</v>
       </c>
       <c r="ER20" s="1" t="n">
-        <v>59.0</v>
+        <v>34.0</v>
       </c>
       <c r="ES20" t="n">
         <v>1.0</v>
@@ -8158,15 +8348,9 @@
       <c r="EU20"/>
       <c r="EV20"/>
       <c r="EW20"/>
-      <c r="EX20" s="3" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="EX20"/>
       <c r="EY20"/>
-      <c r="EZ20" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="EZ20"/>
       <c r="FA20" s="4" t="n">
         <v>43548.0</v>
       </c>
@@ -8174,11 +8358,21 @@
         <v>43548.0</v>
       </c>
       <c r="FC20" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="FD20"/>
-      <c r="FE20"/>
-      <c r="FF20"/>
+        <v>26.0</v>
+      </c>
+      <c r="FD20" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FE20" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="FF20" s="1" t="n">
+        <v>26.0</v>
+      </c>
       <c r="FG20"/>
       <c r="FH20"/>
       <c r="FI20"/>
@@ -8207,10 +8401,22 @@
       <c r="GF20"/>
       <c r="GG20"/>
       <c r="GH20"/>
-      <c r="GI20"/>
-      <c r="GJ20"/>
-      <c r="GK20"/>
-      <c r="GL20"/>
+      <c r="GI20" s="1" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="GJ20" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="GK20" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_ACTUAL</t>
+        </is>
+      </c>
+      <c r="GL20" s="1" t="n">
+        <v>34.0</v>
+      </c>
       <c r="GM20"/>
       <c r="GN20"/>
       <c r="GO20"/>
@@ -8229,7 +8435,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ed4</t>
+          <t>6a32cb6297613a0e4990628b</t>
         </is>
       </c>
       <c r="B21"/>
@@ -8380,24 +8586,24 @@
       <c r="EI21"/>
       <c r="EJ21" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="EK21" s="3" t="inlineStr">
-        <is>
-          <t>D1110</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="EK21"/>
       <c r="EL21"/>
       <c r="EM21"/>
       <c r="EN21"/>
-      <c r="EO21"/>
+      <c r="EO21" s="3" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
       <c r="EP21"/>
       <c r="EQ21" s="1" t="n">
-        <v>73.0</v>
+        <v>99.0</v>
       </c>
       <c r="ER21" s="1" t="n">
-        <v>49.0</v>
+        <v>99.0</v>
       </c>
       <c r="ES21" t="n">
         <v>1.0</v>
@@ -8406,59 +8612,35 @@
       <c r="EU21"/>
       <c r="EV21"/>
       <c r="EW21"/>
-      <c r="EX21"/>
+      <c r="EX21" s="3" t="inlineStr">
+        <is>
+          <t>0023</t>
+        </is>
+      </c>
       <c r="EY21"/>
-      <c r="EZ21"/>
+      <c r="EZ21" t="n">
+        <v>2.0</v>
+      </c>
       <c r="FA21" s="4" t="n">
         <v>43548.0</v>
       </c>
       <c r="FB21" s="4" t="n">
-        <v>43549.0</v>
+        <v>43548.0</v>
       </c>
       <c r="FC21" s="1" t="n">
-        <v>76.0</v>
-      </c>
-      <c r="FD21" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="FE21" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="FF21" s="1" t="n">
-        <v>24.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="FD21"/>
+      <c r="FE21"/>
+      <c r="FF21"/>
       <c r="FG21"/>
-      <c r="FH21" s="3" t="inlineStr">
-        <is>
-          <t>CONTRACTUAL</t>
-        </is>
-      </c>
-      <c r="FI21" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="FJ21" s="1" t="n">
-        <v>25.0</v>
-      </c>
+      <c r="FH21"/>
+      <c r="FI21"/>
+      <c r="FJ21"/>
       <c r="FK21"/>
-      <c r="FL21" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="FM21" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="FN21" s="1" t="n">
-        <v>27.0</v>
-      </c>
+      <c r="FL21"/>
+      <c r="FM21"/>
+      <c r="FN21"/>
       <c r="FO21"/>
       <c r="FP21"/>
       <c r="FQ21"/>
@@ -8479,35 +8661,13 @@
       <c r="GF21"/>
       <c r="GG21"/>
       <c r="GH21"/>
-      <c r="GI21" s="1" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="GJ21" s="3" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="GK21" s="3" t="inlineStr">
-        <is>
-          <t>ALLOWED_ACTUAL</t>
-        </is>
-      </c>
-      <c r="GL21" s="1" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="GM21" s="3" t="inlineStr">
-        <is>
-          <t>KH</t>
-        </is>
-      </c>
-      <c r="GN21" s="3" t="inlineStr">
-        <is>
-          <t>DEDUCTION</t>
-        </is>
-      </c>
-      <c r="GO21" s="1" t="n">
-        <v>50.0</v>
-      </c>
+      <c r="GI21"/>
+      <c r="GJ21"/>
+      <c r="GK21"/>
+      <c r="GL21"/>
+      <c r="GM21"/>
+      <c r="GN21"/>
+      <c r="GO21"/>
       <c r="GP21"/>
       <c r="GQ21"/>
       <c r="GR21"/>
@@ -8523,7 +8683,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>6a04cc591ef26d534baf0ed4</t>
+          <t>6a32cb6297613a0e4990628b</t>
         </is>
       </c>
       <c r="B22"/>
@@ -8674,61 +8834,85 @@
       <c r="EI22"/>
       <c r="EJ22" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="EK22"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="EK22" s="3" t="inlineStr">
+        <is>
+          <t>D1110</t>
+        </is>
+      </c>
       <c r="EL22"/>
       <c r="EM22"/>
       <c r="EN22"/>
       <c r="EO22"/>
-      <c r="EP22" s="3" t="inlineStr">
-        <is>
-          <t>00002143481</t>
-        </is>
-      </c>
+      <c r="EP22"/>
       <c r="EQ22" s="1" t="n">
-        <v>60.0</v>
+        <v>73.0</v>
       </c>
       <c r="ER22" s="1" t="n">
-        <v>59.0</v>
+        <v>-3.0</v>
       </c>
       <c r="ES22" t="n">
-        <v>10.5</v>
+        <v>1.0</v>
       </c>
       <c r="ET22"/>
       <c r="EU22"/>
       <c r="EV22"/>
       <c r="EW22"/>
       <c r="EX22"/>
-      <c r="EY22" s="3" t="inlineStr">
-        <is>
-          <t>00002143482</t>
-        </is>
-      </c>
-      <c r="EZ22" t="n">
-        <v>9.2</v>
-      </c>
+      <c r="EY22"/>
+      <c r="EZ22"/>
       <c r="FA22" s="4" t="n">
         <v>43548.0</v>
       </c>
       <c r="FB22" s="4" t="n">
-        <v>43548.0</v>
+        <v>43549.0</v>
       </c>
       <c r="FC22" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="FD22"/>
-      <c r="FE22"/>
-      <c r="FF22"/>
+        <v>76.0</v>
+      </c>
+      <c r="FD22" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FE22" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="FF22" s="1" t="n">
+        <v>24.0</v>
+      </c>
       <c r="FG22"/>
-      <c r="FH22"/>
-      <c r="FI22"/>
-      <c r="FJ22"/>
+      <c r="FH22" s="3" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL</t>
+        </is>
+      </c>
+      <c r="FI22" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="FJ22" s="1" t="n">
+        <v>25.0</v>
+      </c>
       <c r="FK22"/>
-      <c r="FL22"/>
-      <c r="FM22"/>
-      <c r="FN22"/>
+      <c r="FL22" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="FM22" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="FN22" s="1" t="n">
+        <v>27.0</v>
+      </c>
       <c r="FO22"/>
       <c r="FP22"/>
       <c r="FQ22"/>
@@ -8749,13 +8933,35 @@
       <c r="GF22"/>
       <c r="GG22"/>
       <c r="GH22"/>
-      <c r="GI22"/>
-      <c r="GJ22"/>
-      <c r="GK22"/>
-      <c r="GL22"/>
-      <c r="GM22"/>
-      <c r="GN22"/>
-      <c r="GO22"/>
+      <c r="GI22" s="1" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="GJ22" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="GK22" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED_ACTUAL</t>
+        </is>
+      </c>
+      <c r="GL22" s="1" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="GM22" s="3" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="GN22" s="3" t="inlineStr">
+        <is>
+          <t>DEDUCTION</t>
+        </is>
+      </c>
+      <c r="GO22" s="1" t="n">
+        <v>50.0</v>
+      </c>
       <c r="GP22"/>
       <c r="GQ22"/>
       <c r="GR22"/>
@@ -8768,6 +8974,254 @@
       <c r="GY22"/>
       <c r="GZ22"/>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>6a32cb6297613a0e4990628b</t>
+        </is>
+      </c>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>7722337</t>
+        </is>
+      </c>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>119932404007801</t>
+        </is>
+      </c>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23"/>
+      <c r="AF23"/>
+      <c r="AG23"/>
+      <c r="AH23"/>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23"/>
+      <c r="AL23"/>
+      <c r="AM23"/>
+      <c r="AN23"/>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
+      <c r="AS23"/>
+      <c r="AT23"/>
+      <c r="AU23"/>
+      <c r="AV23"/>
+      <c r="AW23"/>
+      <c r="AX23"/>
+      <c r="AY23"/>
+      <c r="AZ23"/>
+      <c r="BA23"/>
+      <c r="BB23"/>
+      <c r="BC23"/>
+      <c r="BD23"/>
+      <c r="BE23"/>
+      <c r="BF23"/>
+      <c r="BG23"/>
+      <c r="BH23"/>
+      <c r="BI23"/>
+      <c r="BJ23"/>
+      <c r="BK23"/>
+      <c r="BL23"/>
+      <c r="BM23"/>
+      <c r="BN23"/>
+      <c r="BO23"/>
+      <c r="BP23"/>
+      <c r="BQ23"/>
+      <c r="BR23"/>
+      <c r="BS23"/>
+      <c r="BT23"/>
+      <c r="BU23"/>
+      <c r="BV23"/>
+      <c r="BW23"/>
+      <c r="BX23"/>
+      <c r="BY23"/>
+      <c r="BZ23"/>
+      <c r="CA23"/>
+      <c r="CB23"/>
+      <c r="CC23"/>
+      <c r="CD23"/>
+      <c r="CE23"/>
+      <c r="CF23"/>
+      <c r="CG23"/>
+      <c r="CH23"/>
+      <c r="CI23"/>
+      <c r="CJ23"/>
+      <c r="CK23"/>
+      <c r="CL23"/>
+      <c r="CM23"/>
+      <c r="CN23"/>
+      <c r="CO23"/>
+      <c r="CP23"/>
+      <c r="CQ23"/>
+      <c r="CR23"/>
+      <c r="CS23"/>
+      <c r="CT23"/>
+      <c r="CU23"/>
+      <c r="CV23"/>
+      <c r="CW23"/>
+      <c r="CX23"/>
+      <c r="CY23"/>
+      <c r="CZ23"/>
+      <c r="DA23"/>
+      <c r="DB23"/>
+      <c r="DC23"/>
+      <c r="DD23"/>
+      <c r="DE23"/>
+      <c r="DF23"/>
+      <c r="DG23"/>
+      <c r="DH23"/>
+      <c r="DI23"/>
+      <c r="DJ23"/>
+      <c r="DK23"/>
+      <c r="DL23"/>
+      <c r="DM23"/>
+      <c r="DN23"/>
+      <c r="DO23"/>
+      <c r="DP23"/>
+      <c r="DQ23"/>
+      <c r="DR23"/>
+      <c r="DS23"/>
+      <c r="DT23"/>
+      <c r="DU23"/>
+      <c r="DV23"/>
+      <c r="DW23"/>
+      <c r="DX23"/>
+      <c r="DY23"/>
+      <c r="DZ23"/>
+      <c r="EA23"/>
+      <c r="EB23"/>
+      <c r="EC23"/>
+      <c r="ED23"/>
+      <c r="EE23"/>
+      <c r="EF23"/>
+      <c r="EG23"/>
+      <c r="EH23"/>
+      <c r="EI23"/>
+      <c r="EJ23" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="EK23"/>
+      <c r="EL23"/>
+      <c r="EM23"/>
+      <c r="EN23"/>
+      <c r="EO23"/>
+      <c r="EP23" s="3" t="inlineStr">
+        <is>
+          <t>00002143481</t>
+        </is>
+      </c>
+      <c r="EQ23" s="1" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="ER23" s="1" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="ES23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="ET23"/>
+      <c r="EU23"/>
+      <c r="EV23"/>
+      <c r="EW23"/>
+      <c r="EX23"/>
+      <c r="EY23" s="3" t="inlineStr">
+        <is>
+          <t>00002143482</t>
+        </is>
+      </c>
+      <c r="EZ23" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="FA23" s="4" t="n">
+        <v>43548.0</v>
+      </c>
+      <c r="FB23" s="4" t="n">
+        <v>43548.0</v>
+      </c>
+      <c r="FC23" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="FD23"/>
+      <c r="FE23"/>
+      <c r="FF23"/>
+      <c r="FG23"/>
+      <c r="FH23"/>
+      <c r="FI23"/>
+      <c r="FJ23"/>
+      <c r="FK23"/>
+      <c r="FL23"/>
+      <c r="FM23"/>
+      <c r="FN23"/>
+      <c r="FO23"/>
+      <c r="FP23"/>
+      <c r="FQ23"/>
+      <c r="FR23"/>
+      <c r="FS23"/>
+      <c r="FT23"/>
+      <c r="FU23"/>
+      <c r="FV23"/>
+      <c r="FW23"/>
+      <c r="FX23"/>
+      <c r="FY23"/>
+      <c r="FZ23"/>
+      <c r="GA23"/>
+      <c r="GB23"/>
+      <c r="GC23"/>
+      <c r="GD23"/>
+      <c r="GE23"/>
+      <c r="GF23"/>
+      <c r="GG23"/>
+      <c r="GH23"/>
+      <c r="GI23"/>
+      <c r="GJ23"/>
+      <c r="GK23"/>
+      <c r="GL23"/>
+      <c r="GM23"/>
+      <c r="GN23"/>
+      <c r="GO23"/>
+      <c r="GP23"/>
+      <c r="GQ23"/>
+      <c r="GR23"/>
+      <c r="GS23"/>
+      <c r="GT23"/>
+      <c r="GU23"/>
+      <c r="GV23"/>
+      <c r="GW23"/>
+      <c r="GX23"/>
+      <c r="GY23"/>
+      <c r="GZ23"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
